--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9855</v>
       </c>
       <c r="F2" t="n">
-        <v>68.7453</v>
+        <v>70.33839999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>203.4208</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9856</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>70.18899999999999</v>
+        <v>71.1319</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>196.3833</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9697</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>101.4029</v>
+        <v>101.4419</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>239.3684</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8766</v>
+        <v>0.8773</v>
       </c>
       <c r="F5" t="n">
-        <v>192.8743</v>
+        <v>192.7845</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>333.2888</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8778</v>
+        <v>0.8784</v>
       </c>
       <c r="F6" t="n">
-        <v>193.2295</v>
+        <v>193.1334</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>329.036</v>
       </c>
     </row>
     <row r="7">
@@ -614,17 +614,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9705</v>
+        <v>0.9548</v>
       </c>
       <c r="F7" t="n">
-        <v>91.15000000000001</v>
+        <v>110.5537</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>202.5303</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9701</v>
+        <v>0.9699</v>
       </c>
       <c r="F8" t="n">
-        <v>94.69629999999999</v>
+        <v>95.04349999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>220.1135</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9802</v>
+        <v>0.9847</v>
       </c>
       <c r="F9" t="n">
-        <v>79.8639</v>
+        <v>70.54770000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>205.6857</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9698</v>
+        <v>0.9695</v>
       </c>
       <c r="F10" t="n">
-        <v>95.07040000000001</v>
+        <v>95.45740000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>220.7184</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9692</v>
+        <v>0.9689</v>
       </c>
       <c r="F11" t="n">
-        <v>95.76690000000001</v>
+        <v>95.9791</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>220.0607</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9678</v>
+        <v>0.9675</v>
       </c>
       <c r="F12" t="n">
-        <v>97.34999999999999</v>
+        <v>97.7591</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>219.6967</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9485</v>
+        <v>0.9677</v>
       </c>
       <c r="F13" t="n">
-        <v>121.2329</v>
+        <v>98.13630000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>218.6378</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +817,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.969</v>
       </c>
       <c r="F14" t="n">
-        <v>95.68429999999999</v>
+        <v>96.0475</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>220.3833</v>
       </c>
     </row>
     <row r="15">
@@ -846,17 +846,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9681</v>
+        <v>0.9678</v>
       </c>
       <c r="F15" t="n">
-        <v>96.98909999999999</v>
+        <v>97.2657</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>219.9646</v>
       </c>
     </row>
     <row r="16">
@@ -875,17 +875,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9489</v>
+        <v>0.9794</v>
       </c>
       <c r="F16" t="n">
-        <v>120.9611</v>
+        <v>79.8015</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>220.093</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>0.9678</v>
       </c>
       <c r="F17" t="n">
-        <v>98.24250000000001</v>
+        <v>98.0651</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>217.4327</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9853</v>
+        <v>0.9848</v>
       </c>
       <c r="F18" t="n">
-        <v>69.2608</v>
+        <v>69.6554</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>203.4128</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9866</v>
+        <v>0.9842</v>
       </c>
       <c r="F19" t="n">
-        <v>69.72709999999999</v>
+        <v>71.7522</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>203.4712</v>
       </c>
     </row>
     <row r="20">
@@ -991,17 +991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.985</v>
+        <v>0.9768</v>
       </c>
       <c r="F20" t="n">
-        <v>73.37050000000001</v>
+        <v>87.848</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>205.5041</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9769</v>
       </c>
       <c r="F21" t="n">
-        <v>80.75839999999999</v>
+        <v>88.27070000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>205.1437</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.978</v>
+        <v>0.9811</v>
       </c>
       <c r="F22" t="n">
-        <v>82.23399999999999</v>
+        <v>77.0121</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>205.1959</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9855</v>
+        <v>0.9853</v>
       </c>
       <c r="F23" t="n">
-        <v>72.6888</v>
+        <v>73.16719999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>201.7618</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9867</v>
+        <v>0.9852</v>
       </c>
       <c r="F24" t="n">
-        <v>67.47620000000001</v>
+        <v>71.9623</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>202.3404</v>
       </c>
     </row>
     <row r="25">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9867</v>
+        <v>0.9868</v>
       </c>
       <c r="F25" t="n">
-        <v>66.2998</v>
+        <v>65.9478</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>204.7296</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9802</v>
+        <v>0.9797</v>
       </c>
       <c r="F26" t="n">
-        <v>78.2666</v>
+        <v>78.37909999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>202.5314</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>0.9861</v>
       </c>
       <c r="F27" t="n">
-        <v>66.7225</v>
+        <v>66.93210000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>204.8939</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.98</v>
+        <v>0.9805</v>
       </c>
       <c r="F28" t="n">
-        <v>78.8373</v>
+        <v>77.9609</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>202.0641</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9799</v>
+        <v>0.9861</v>
       </c>
       <c r="F29" t="n">
-        <v>81.3845</v>
+        <v>71.4833</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>205.4297</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>0.9856</v>
       </c>
       <c r="F30" t="n">
-        <v>71.3917</v>
+        <v>71.801</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>204.4992</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9868</v>
+        <v>0.9866</v>
       </c>
       <c r="F31" t="n">
-        <v>68.7636</v>
+        <v>69.00620000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>202.4475</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.98</v>
+        <v>0.9799</v>
       </c>
       <c r="F32" t="n">
-        <v>81.12730000000001</v>
+        <v>81.27760000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>206.2081</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9795</v>
+        <v>0.9856</v>
       </c>
       <c r="F33" t="n">
-        <v>82.3236</v>
+        <v>70.83750000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>205.8494</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9862</v>
+        <v>0.9818</v>
       </c>
       <c r="F34" t="n">
-        <v>71.32389999999999</v>
+        <v>78.1093</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>204.8343</v>
       </c>
     </row>
     <row r="35">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9858</v>
+        <v>0.9855</v>
       </c>
       <c r="F35" t="n">
-        <v>68.24939999999999</v>
+        <v>67.77549999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>202.5374</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>0.9866</v>
       </c>
       <c r="F36" t="n">
-        <v>69.6403</v>
+        <v>69.6146</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>205.9353</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9867</v>
+        <v>0.9866</v>
       </c>
       <c r="F37" t="n">
-        <v>69.1895</v>
+        <v>69.27379999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>200.0682</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9875</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>67.1142</v>
+        <v>67.40949999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>199.2216</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.979</v>
+        <v>0.9797</v>
       </c>
       <c r="F39" t="n">
-        <v>82.1251</v>
+        <v>81.07810000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>202.0184</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>0.9787</v>
       </c>
       <c r="F40" t="n">
-        <v>83.19159999999999</v>
+        <v>83.6001</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>200.601</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.982</v>
       </c>
       <c r="F41" t="n">
-        <v>71.2452</v>
+        <v>77.7141</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>203.9835</v>
       </c>
     </row>
     <row r="42">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9856</v>
       </c>
       <c r="F42" t="n">
-        <v>77.3464</v>
+        <v>68.2711</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>203.189</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>0.9866</v>
       </c>
       <c r="F43" t="n">
-        <v>69.6523</v>
+        <v>69.6247</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>205.6807</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9865</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>69.3742</v>
+        <v>69.5001</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>200.4156</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9875</v>
       </c>
       <c r="F45" t="n">
-        <v>67.1512</v>
+        <v>67.37430000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>199.038</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9851</v>
+        <v>0.9801</v>
       </c>
       <c r="F46" t="n">
-        <v>69.6915</v>
+        <v>80.1495</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>203.0775</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9872</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>67.12130000000001</v>
+        <v>83.2957</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>200.9857</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9866</v>
       </c>
       <c r="F48" t="n">
-        <v>70.81140000000001</v>
+        <v>70.6643</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>207.4157</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9859</v>
+        <v>0.9867</v>
       </c>
       <c r="F49" t="n">
-        <v>72.91670000000001</v>
+        <v>70.53279999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>205.6672</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9161</v>
+        <v>0.9147</v>
       </c>
       <c r="F50" t="n">
-        <v>171.49</v>
+        <v>172.0859</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>327.7899</v>
       </c>
     </row>
     <row r="51">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8913</v>
+        <v>0.891</v>
       </c>
       <c r="F51" t="n">
-        <v>191.2179</v>
+        <v>191.2855</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>317.8124</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8877</v>
+        <v>0.8869</v>
       </c>
       <c r="F52" t="n">
-        <v>190.675</v>
+        <v>191.0158</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>315.6412</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8694</v>
+        <v>0.8692</v>
       </c>
       <c r="F53" t="n">
-        <v>210.6447</v>
+        <v>210.6494</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>327.8794</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8635</v>
+        <v>0.8632</v>
       </c>
       <c r="F54" t="n">
-        <v>207.834</v>
+        <v>207.9136</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>321.0637</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8677</v>
+        <v>0.8679</v>
       </c>
       <c r="F55" t="n">
-        <v>202.9514</v>
+        <v>202.971</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>320.991</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>0.9404</v>
       </c>
       <c r="F56" t="n">
-        <v>155.9711</v>
+        <v>155.8354</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>319.6564</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9075</v>
+        <v>0.9073</v>
       </c>
       <c r="F57" t="n">
-        <v>178.45</v>
+        <v>178.3915</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>320.2063</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8789</v>
+        <v>0.8794</v>
       </c>
       <c r="F58" t="n">
-        <v>192.9675</v>
+        <v>192.779</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>330.3112</v>
       </c>
     </row>
     <row r="59">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8782</v>
+        <v>0.8789</v>
       </c>
       <c r="F59" t="n">
-        <v>192.6442</v>
+        <v>192.4741</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>330.3814</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.879</v>
+        <v>0.88</v>
       </c>
       <c r="F60" t="n">
-        <v>191.9346</v>
+        <v>191.5402</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>330.6573</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.879</v>
+        <v>0.8802</v>
       </c>
       <c r="F61" t="n">
-        <v>191.4116</v>
+        <v>190.9943</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>329.4402</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8529</v>
+        <v>0.8531</v>
       </c>
       <c r="F62" t="n">
-        <v>207.7483</v>
+        <v>207.6958</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>325.6704</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8988</v>
+        <v>0.8993</v>
       </c>
       <c r="F63" t="n">
-        <v>181.8195</v>
+        <v>181.7513</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>323.3533</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.854</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>207.2948</v>
+        <v>207.2294</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>324.3955</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.8941</v>
       </c>
       <c r="F65" t="n">
-        <v>183.7498</v>
+        <v>183.5636</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>326.6045</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9018</v>
+        <v>0.9172</v>
       </c>
       <c r="F66" t="n">
-        <v>186.5622</v>
+        <v>172.2683</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>322.355</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9132</v>
+        <v>0.9123</v>
       </c>
       <c r="F67" t="n">
-        <v>176.347</v>
+        <v>176.667</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>317.8137</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9258</v>
+        <v>0.9254</v>
       </c>
       <c r="F68" t="n">
-        <v>163.0451</v>
+        <v>163.1921</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>321.0864</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9828</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>74.0711</v>
+        <v>75.047</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>188.7925</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9855</v>
+        <v>0.9792</v>
       </c>
       <c r="F70" t="n">
-        <v>69.4804</v>
+        <v>81.8429</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>192.2299</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.985</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>69.9944</v>
+        <v>70.7718</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>188.7751</v>
       </c>
     </row>
     <row r="72">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9856</v>
       </c>
       <c r="F72" t="n">
-        <v>68.1486</v>
+        <v>70.54040000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>189.5521</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9633</v>
       </c>
       <c r="F73" t="n">
-        <v>106.7554</v>
+        <v>106.5844</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>206.1392</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9815</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>77.5647</v>
+        <v>85.7008</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>212.2481</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.97</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>94.4237</v>
+        <v>79.4229</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>227.4657</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.97</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>94.4237</v>
+        <v>79.4229</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>227.4657</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>0.9068000000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>172.617</v>
+        <v>172.6373</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>325.4957</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9084</v>
+        <v>0.9087</v>
       </c>
       <c r="F78" t="n">
-        <v>172.0196</v>
+        <v>171.2347</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>324.7849</v>
       </c>
     </row>
     <row r="79">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9061</v>
+        <v>0.9062</v>
       </c>
       <c r="F79" t="n">
-        <v>173.4079</v>
+        <v>173.7944</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>326.0319</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9081</v>
+        <v>0.9086</v>
       </c>
       <c r="F80" t="n">
-        <v>172.1101</v>
+        <v>171.2501</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>324.6752</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9166</v>
+        <v>0.9165</v>
       </c>
       <c r="F81" t="n">
-        <v>169.217</v>
+        <v>169.5574</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>323.0939</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8597</v>
+        <v>0.8595</v>
       </c>
       <c r="F82" t="n">
-        <v>206.059</v>
+        <v>206.1442</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>328.3126</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9731</v>
+        <v>0.9799</v>
       </c>
       <c r="F83" t="n">
-        <v>88.1371</v>
+        <v>77.8488</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>227.5433</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9805</v>
+        <v>0.9799</v>
       </c>
       <c r="F84" t="n">
-        <v>76.44880000000001</v>
+        <v>77.5427</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>224.972</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.973</v>
+        <v>0.98</v>
       </c>
       <c r="F85" t="n">
-        <v>88.2929</v>
+        <v>77.7415</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>227.1747</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9799</v>
+        <v>0.9811</v>
       </c>
       <c r="F86" t="n">
-        <v>79.3094</v>
+        <v>76.7372</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>202.8792</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.979</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>80.46250000000001</v>
+        <v>81.6497</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>200.1561</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9835</v>
       </c>
       <c r="F88" t="n">
-        <v>73.73699999999999</v>
+        <v>73.44750000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>205.7982</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9846</v>
+        <v>0.9855</v>
       </c>
       <c r="F89" t="n">
-        <v>72.18819999999999</v>
+        <v>70.6884</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>199.1506</v>
       </c>
     </row>
     <row r="90">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9866</v>
+        <v>0.9867</v>
       </c>
       <c r="F90" t="n">
-        <v>69.6653</v>
+        <v>69.5878</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>205.6845</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9865</v>
+        <v>0.9863</v>
       </c>
       <c r="F91" t="n">
-        <v>69.398</v>
+        <v>69.5445</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>200.3979</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9835</v>
       </c>
       <c r="F92" t="n">
-        <v>73.73699999999999</v>
+        <v>73.44750000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>205.7982</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9865</v>
+        <v>0.9863</v>
       </c>
       <c r="F93" t="n">
-        <v>69.398</v>
+        <v>69.5445</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>200.3979</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9697</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F94" t="n">
-        <v>101.4029</v>
+        <v>101.4419</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>239.3684</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7947</v>
+        <v>0.795</v>
       </c>
       <c r="F95" t="n">
-        <v>256.5077</v>
+        <v>256.4459</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>379.5158</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9697</v>
+        <v>0.9694</v>
       </c>
       <c r="F96" t="n">
-        <v>101.1775</v>
+        <v>101.3403</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>240.5206</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9698</v>
+        <v>0.9695</v>
       </c>
       <c r="F97" t="n">
-        <v>101.518</v>
+        <v>101.5737</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>240.6538</v>
       </c>
     </row>
     <row r="98">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9833</v>
+        <v>0.9842</v>
       </c>
       <c r="F98" t="n">
-        <v>76.57170000000001</v>
+        <v>76.3492</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>208.9743</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.982</v>
+        <v>0.9823</v>
       </c>
       <c r="F99" t="n">
-        <v>80.4528</v>
+        <v>79.6142</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>212.6565</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9828</v>
+        <v>0.9826</v>
       </c>
       <c r="F100" t="n">
-        <v>78.8811</v>
+        <v>79.2786</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>209.6822</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9837</v>
       </c>
       <c r="F101" t="n">
-        <v>76.36279999999999</v>
+        <v>75.9593</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>214.3939</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.984</v>
+        <v>0.9836</v>
       </c>
       <c r="F102" t="n">
-        <v>75.7997</v>
+        <v>77.1332</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>215.6439</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9845</v>
+        <v>0.9749</v>
       </c>
       <c r="F103" t="n">
-        <v>79.3586</v>
+        <v>92.40689999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>216.9149</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9819</v>
+        <v>0.982</v>
       </c>
       <c r="F104" t="n">
-        <v>79.7557</v>
+        <v>79.4657</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>208.6535</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9838</v>
+        <v>0.9832</v>
       </c>
       <c r="F105" t="n">
-        <v>77.4843</v>
+        <v>78.9911</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>211.321</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9825</v>
+        <v>0.9827</v>
       </c>
       <c r="F106" t="n">
-        <v>79.15649999999999</v>
+        <v>78.9289</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>213.511</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9813</v>
+        <v>0.9819</v>
       </c>
       <c r="F107" t="n">
-        <v>80.40600000000001</v>
+        <v>79.1541</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>212.8529</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>0.9837</v>
       </c>
       <c r="F108" t="n">
-        <v>80.9087</v>
+        <v>80.017</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>217.9581</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9852</v>
       </c>
       <c r="F109" t="n">
-        <v>75.678</v>
+        <v>76.0629</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>210.014</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E110" t="n">
         <v>0.9817</v>
       </c>
       <c r="F110" t="n">
-        <v>79.3623</v>
+        <v>79.08280000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>200.3983</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9865</v>
+        <v>0.9832</v>
       </c>
       <c r="F111" t="n">
-        <v>72.59690000000001</v>
+        <v>75.1728</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>204.4003</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9841</v>
+        <v>0.9843</v>
       </c>
       <c r="F112" t="n">
-        <v>80.08620000000001</v>
+        <v>79.026</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>216.4683</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9862</v>
+        <v>0.9858</v>
       </c>
       <c r="F113" t="n">
-        <v>74.14109999999999</v>
+        <v>75.16840000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>208.4015</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9816</v>
+        <v>0.9817</v>
       </c>
       <c r="F114" t="n">
-        <v>79.49160000000001</v>
+        <v>79.31789999999999</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>200.5555</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9799</v>
+        <v>0.9823</v>
       </c>
       <c r="F115" t="n">
-        <v>83.28360000000001</v>
+        <v>76.8205</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>206.9118</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8435</v>
+        <v>0.8433</v>
       </c>
       <c r="F116" t="n">
-        <v>215.4258</v>
+        <v>215.4715</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>329.4887</v>
       </c>
     </row>
     <row r="117">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8652</v>
+        <v>0.8839</v>
       </c>
       <c r="F117" t="n">
-        <v>200.4305</v>
+        <v>192.3805</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>331.4326</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9838</v>
+        <v>0.9832</v>
       </c>
       <c r="F118" t="n">
-        <v>77.4843</v>
+        <v>78.9911</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>211.321</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9862</v>
+        <v>0.9858</v>
       </c>
       <c r="F119" t="n">
-        <v>74.14109999999999</v>
+        <v>75.16840000000001</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>208.4015</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9494</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>116.6751</v>
+        <v>116.943</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>209.7527</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9494</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>116.6751</v>
+        <v>116.943</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>209.7527</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9855</v>
+        <v>0.9853</v>
       </c>
       <c r="F122" t="n">
-        <v>66.986</v>
+        <v>67.282</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>183.8576</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9862</v>
+        <v>0.9858</v>
       </c>
       <c r="F123" t="n">
-        <v>74.74720000000001</v>
+        <v>75.6384</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>208.9034</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9867</v>
+        <v>0.9865</v>
       </c>
       <c r="F124" t="n">
-        <v>73.7055</v>
+        <v>74.0454</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>209.2376</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9349</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>136.3032</v>
+        <v>100.2053</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>240.7978</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9788</v>
+        <v>0.9786</v>
       </c>
       <c r="F126" t="n">
-        <v>81.1598</v>
+        <v>81.2277</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>199.1046</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.7874</v>
+        <v>0.7876</v>
       </c>
       <c r="F127" t="n">
-        <v>238.9343</v>
+        <v>238.9323</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>353.5263</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9775</v>
+        <v>0.9774</v>
       </c>
       <c r="F128" t="n">
-        <v>82.3856</v>
+        <v>82.5391</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>200.1882</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9776</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>82.0596</v>
+        <v>82.48269999999999</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>200.1315</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9772</v>
+        <v>0.9771</v>
       </c>
       <c r="F130" t="n">
-        <v>82.74679999999999</v>
+        <v>83.0489</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>201.4761</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9771</v>
+        <v>0.9772</v>
       </c>
       <c r="F131" t="n">
-        <v>82.6549</v>
+        <v>82.77419999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>200.6486</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9777</v>
+        <v>0.9848</v>
       </c>
       <c r="F132" t="n">
-        <v>81.8652</v>
+        <v>70.19029999999999</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>197.731</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9772</v>
+        <v>0.9835</v>
       </c>
       <c r="F133" t="n">
-        <v>82.28789999999999</v>
+        <v>71.7961</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>199.3757</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9778</v>
+        <v>0.9779</v>
       </c>
       <c r="F134" t="n">
-        <v>81.60129999999999</v>
+        <v>81.6867</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>199.6845</v>
       </c>
     </row>
     <row r="135">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9775</v>
+        <v>0.9776</v>
       </c>
       <c r="F135" t="n">
-        <v>82.4033</v>
+        <v>82.2086</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>200.1325</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9774</v>
       </c>
       <c r="F136" t="n">
-        <v>82.42870000000001</v>
+        <v>82.4747</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>200.3094</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9789</v>
+        <v>0.9791</v>
       </c>
       <c r="F137" t="n">
-        <v>81.04000000000001</v>
+        <v>80.8704</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>198.7059</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E138" t="n">
         <v>0.9861</v>
       </c>
       <c r="F138" t="n">
-        <v>68.4777</v>
+        <v>68.3527</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>199.7458</v>
       </c>
     </row>
     <row r="139">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9856</v>
+        <v>0.9862</v>
       </c>
       <c r="F139" t="n">
-        <v>68.8861</v>
+        <v>68.35290000000001</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>200.1827</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.98</v>
+        <v>0.9804</v>
       </c>
       <c r="F140" t="n">
-        <v>82.00700000000001</v>
+        <v>81.4551</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>196.2966</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.98</v>
+        <v>0.9801</v>
       </c>
       <c r="F141" t="n">
-        <v>82.063</v>
+        <v>81.9294</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>194.4432</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E142" t="n">
         <v>0.9861</v>
       </c>
       <c r="F142" t="n">
-        <v>68.4777</v>
+        <v>68.3527</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>199.7458</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E143" t="n">
         <v>0.9863</v>
       </c>
       <c r="F143" t="n">
-        <v>68.011</v>
+        <v>67.7602</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>198.7855</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9846</v>
+        <v>0.9849</v>
       </c>
       <c r="F144" t="n">
-        <v>70.5591</v>
+        <v>70.9256</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>197.0597</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.98</v>
+        <v>0.9801</v>
       </c>
       <c r="F145" t="n">
-        <v>82.063</v>
+        <v>81.9294</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>194.4432</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
         <v>0.7882</v>
       </c>
       <c r="F146" t="n">
-        <v>238.2962</v>
+        <v>238.3036</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>353.7653</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.7897</v>
+        <v>0.79</v>
       </c>
       <c r="F147" t="n">
-        <v>237.7587</v>
+        <v>237.7503</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>353.5388</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
         <v>0.7895</v>
       </c>
       <c r="F148" t="n">
-        <v>238.1654</v>
+        <v>238.2072</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>353.1922</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.7906</v>
+        <v>0.7907</v>
       </c>
       <c r="F149" t="n">
-        <v>237.7094</v>
+        <v>237.7169</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>353.1731</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.7885</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="F150" t="n">
-        <v>238.3872</v>
+        <v>238.3628</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>353.7547</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.7887</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="F151" t="n">
-        <v>238.3237</v>
+        <v>238.3192</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>353.8684</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.7895</v>
+        <v>0.7896</v>
       </c>
       <c r="F152" t="n">
-        <v>237.8612</v>
+        <v>237.8898</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>353.8741</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E153" t="n">
         <v>0.7903</v>
       </c>
       <c r="F153" t="n">
-        <v>237.6251</v>
+        <v>237.6603</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>353.7078</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.7892</v>
+        <v>0.7891</v>
       </c>
       <c r="F154" t="n">
-        <v>238.1518</v>
+        <v>238.2105</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>352.337</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.904</v>
+        <v>0.9042</v>
       </c>
       <c r="F155" t="n">
-        <v>178.9374</v>
+        <v>179.1117</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>320.8706</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9105</v>
+        <v>0.9102</v>
       </c>
       <c r="F156" t="n">
-        <v>172.6011</v>
+        <v>172.9713</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>323.0295</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.9063</v>
       </c>
       <c r="F157" t="n">
-        <v>174.7656</v>
+        <v>175.1256</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>324.9524</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8779</v>
+        <v>0.878</v>
       </c>
       <c r="F158" t="n">
-        <v>200.4513</v>
+        <v>200.4145</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>324.2083</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9862</v>
+        <v>0.986</v>
       </c>
       <c r="F159" t="n">
-        <v>66.10250000000001</v>
+        <v>67.0766</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>190.2741</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8741</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="F160" t="n">
-        <v>197.6122</v>
+        <v>197.9142</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>339.1699</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8882</v>
+        <v>0.8729</v>
       </c>
       <c r="F161" t="n">
-        <v>189.244</v>
+        <v>198.1167</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>341.2114</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9781</v>
+        <v>0.9782</v>
       </c>
       <c r="F162" t="n">
-        <v>81.5921</v>
+        <v>81.43689999999999</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>187.3425</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E163" t="n">
         <v>0.9808</v>
       </c>
       <c r="F163" t="n">
-        <v>78.5819</v>
+        <v>78.1712</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>194.0708</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.98</v>
+        <v>0.9804</v>
       </c>
       <c r="F164" t="n">
-        <v>82.0097</v>
+        <v>81.45780000000001</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>196.3186</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9349</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="F165" t="n">
-        <v>136.3032</v>
+        <v>100.2053</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>240.7978</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7933</v>
+        <v>0.7937</v>
       </c>
       <c r="F166" t="n">
-        <v>256.5794</v>
+        <v>256.5079</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>379.2027</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9768</v>
+        <v>0.9771</v>
       </c>
       <c r="F167" t="n">
-        <v>83.7741</v>
+        <v>83.23520000000001</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>200.5324</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9876</v>
+        <v>0.9869</v>
       </c>
       <c r="F168" t="n">
-        <v>67.759</v>
+        <v>67.7345</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>193.3371</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9822</v>
+        <v>0.9856</v>
       </c>
       <c r="F169" t="n">
-        <v>78.5958</v>
+        <v>70.9252</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>205.1854</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9745</v>
+        <v>0.9791</v>
       </c>
       <c r="F170" t="n">
-        <v>94.72239999999999</v>
+        <v>86.00060000000001</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>215.0183</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9832</v>
+        <v>0.9836</v>
       </c>
       <c r="F171" t="n">
-        <v>75.9503</v>
+        <v>74.48860000000001</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>211.0028</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9849</v>
+        <v>0.9851</v>
       </c>
       <c r="F172" t="n">
-        <v>70.0254</v>
+        <v>69.51220000000001</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>196.1808</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9855</v>
       </c>
       <c r="F2" t="n">
+        <v>1.3182</v>
+      </c>
+      <c r="G2" t="n">
         <v>70.33839999999999</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>203.4208</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F3" t="n">
+        <v>1.2966</v>
+      </c>
+      <c r="G3" t="n">
         <v>71.1319</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>196.3833</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.9693000000000001</v>
       </c>
       <c r="F4" t="n">
+        <v>1.4406</v>
+      </c>
+      <c r="G4" t="n">
         <v>101.4419</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>239.3684</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.8773</v>
       </c>
       <c r="F5" t="n">
+        <v>1.8542</v>
+      </c>
+      <c r="G5" t="n">
         <v>192.7845</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>333.2888</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.8784</v>
       </c>
       <c r="F6" t="n">
+        <v>1.8326</v>
+      </c>
+      <c r="G6" t="n">
         <v>193.1334</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>329.036</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.9548</v>
       </c>
       <c r="F7" t="n">
+        <v>1.3154</v>
+      </c>
+      <c r="G7" t="n">
         <v>110.5537</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>202.5303</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.9699</v>
       </c>
       <c r="F8" t="n">
+        <v>1.3726</v>
+      </c>
+      <c r="G8" t="n">
         <v>95.04349999999999</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>220.1135</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.9847</v>
       </c>
       <c r="F9" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="G9" t="n">
         <v>70.54770000000001</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>205.6857</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.9695</v>
       </c>
       <c r="F10" t="n">
+        <v>1.3746</v>
+      </c>
+      <c r="G10" t="n">
         <v>95.45740000000001</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>220.7184</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.9689</v>
       </c>
       <c r="F11" t="n">
+        <v>1.3724</v>
+      </c>
+      <c r="G11" t="n">
         <v>95.9791</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>220.0607</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.9675</v>
       </c>
       <c r="F12" t="n">
+        <v>1.3712</v>
+      </c>
+      <c r="G12" t="n">
         <v>97.7591</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>219.6967</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.9677</v>
       </c>
       <c r="F13" t="n">
+        <v>1.3676</v>
+      </c>
+      <c r="G13" t="n">
         <v>98.13630000000001</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>218.6378</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.969</v>
       </c>
       <c r="F14" t="n">
+        <v>1.3735</v>
+      </c>
+      <c r="G14" t="n">
         <v>96.0475</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>220.3833</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.9678</v>
       </c>
       <c r="F15" t="n">
+        <v>1.3721</v>
+      </c>
+      <c r="G15" t="n">
         <v>97.2657</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>219.9646</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.9794</v>
       </c>
       <c r="F16" t="n">
+        <v>1.3725</v>
+      </c>
+      <c r="G16" t="n">
         <v>79.8015</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>220.093</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.9678</v>
       </c>
       <c r="F17" t="n">
+        <v>1.3636</v>
+      </c>
+      <c r="G17" t="n">
         <v>98.0651</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>217.4327</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.9848</v>
       </c>
       <c r="F18" t="n">
+        <v>1.3182</v>
+      </c>
+      <c r="G18" t="n">
         <v>69.6554</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>203.4128</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.9842</v>
       </c>
       <c r="F19" t="n">
+        <v>1.3184</v>
+      </c>
+      <c r="G19" t="n">
         <v>71.7522</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>203.4712</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9768</v>
       </c>
       <c r="F20" t="n">
+        <v>1.3248</v>
+      </c>
+      <c r="G20" t="n">
         <v>87.848</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>205.5041</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.9769</v>
       </c>
       <c r="F21" t="n">
+        <v>1.3236</v>
+      </c>
+      <c r="G21" t="n">
         <v>88.27070000000001</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>205.1437</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9811</v>
       </c>
       <c r="F22" t="n">
+        <v>1.3238</v>
+      </c>
+      <c r="G22" t="n">
         <v>77.0121</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>205.1959</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.9853</v>
       </c>
       <c r="F23" t="n">
+        <v>1.3131</v>
+      </c>
+      <c r="G23" t="n">
         <v>73.16719999999999</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>201.7618</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.9852</v>
       </c>
       <c r="F24" t="n">
+        <v>1.3148</v>
+      </c>
+      <c r="G24" t="n">
         <v>71.9623</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>202.3404</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.9868</v>
       </c>
       <c r="F25" t="n">
+        <v>1.3223</v>
+      </c>
+      <c r="G25" t="n">
         <v>65.9478</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>204.7296</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.9797</v>
       </c>
       <c r="F26" t="n">
+        <v>1.3154</v>
+      </c>
+      <c r="G26" t="n">
         <v>78.37909999999999</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>202.5314</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9861</v>
       </c>
       <c r="F27" t="n">
+        <v>1.3228</v>
+      </c>
+      <c r="G27" t="n">
         <v>66.93210000000001</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>204.8939</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.9805</v>
       </c>
       <c r="F28" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="G28" t="n">
         <v>77.9609</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>202.0641</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9861</v>
       </c>
       <c r="F29" t="n">
+        <v>1.3245</v>
+      </c>
+      <c r="G29" t="n">
         <v>71.4833</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>205.4297</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9856</v>
       </c>
       <c r="F30" t="n">
+        <v>1.3216</v>
+      </c>
+      <c r="G30" t="n">
         <v>71.801</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>204.4992</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9866</v>
       </c>
       <c r="F31" t="n">
+        <v>1.3152</v>
+      </c>
+      <c r="G31" t="n">
         <v>69.00620000000001</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>202.4475</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.9799</v>
       </c>
       <c r="F32" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="G32" t="n">
         <v>81.27760000000001</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>206.2081</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9856</v>
       </c>
       <c r="F33" t="n">
+        <v>1.3259</v>
+      </c>
+      <c r="G33" t="n">
         <v>70.83750000000001</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>205.8494</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9818</v>
       </c>
       <c r="F34" t="n">
+        <v>1.3227</v>
+      </c>
+      <c r="G34" t="n">
         <v>78.1093</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>204.8343</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9855</v>
       </c>
       <c r="F35" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="G35" t="n">
         <v>67.77549999999999</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>202.5374</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.9866</v>
       </c>
       <c r="F36" t="n">
+        <v>1.3261</v>
+      </c>
+      <c r="G36" t="n">
         <v>69.6146</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>205.9353</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.9866</v>
       </c>
       <c r="F37" t="n">
+        <v>1.3078</v>
+      </c>
+      <c r="G37" t="n">
         <v>69.27379999999999</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>200.0682</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9874000000000001</v>
       </c>
       <c r="F38" t="n">
+        <v>1.3052</v>
+      </c>
+      <c r="G38" t="n">
         <v>67.40949999999999</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>199.2216</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.9797</v>
       </c>
       <c r="F39" t="n">
+        <v>1.3138</v>
+      </c>
+      <c r="G39" t="n">
         <v>81.07810000000001</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>202.0184</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.9787</v>
       </c>
       <c r="F40" t="n">
+        <v>1.3095</v>
+      </c>
+      <c r="G40" t="n">
         <v>83.6001</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>200.601</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.982</v>
       </c>
       <c r="F41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G41" t="n">
         <v>77.7141</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>203.9835</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9856</v>
       </c>
       <c r="F42" t="n">
+        <v>1.3175</v>
+      </c>
+      <c r="G42" t="n">
         <v>68.2711</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>203.189</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.9866</v>
       </c>
       <c r="F43" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="G43" t="n">
         <v>69.6247</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>205.6807</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9864000000000001</v>
       </c>
       <c r="F44" t="n">
+        <v>1.3089</v>
+      </c>
+      <c r="G44" t="n">
         <v>69.5001</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>200.4156</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9875</v>
       </c>
       <c r="F45" t="n">
+        <v>1.3047</v>
+      </c>
+      <c r="G45" t="n">
         <v>67.37430000000001</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>199.038</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9801</v>
       </c>
       <c r="F46" t="n">
+        <v>1.3171</v>
+      </c>
+      <c r="G46" t="n">
         <v>80.1495</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>203.0775</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.9792999999999999</v>
       </c>
       <c r="F47" t="n">
+        <v>1.3106</v>
+      </c>
+      <c r="G47" t="n">
         <v>83.2957</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>200.9857</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.9866</v>
       </c>
       <c r="F48" t="n">
+        <v>1.3308</v>
+      </c>
+      <c r="G48" t="n">
         <v>70.6643</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>207.4157</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9867</v>
       </c>
       <c r="F49" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="G49" t="n">
         <v>70.53279999999999</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>205.6672</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.9147</v>
       </c>
       <c r="F50" t="n">
+        <v>1.8263</v>
+      </c>
+      <c r="G50" t="n">
         <v>172.0859</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>327.7899</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.891</v>
       </c>
       <c r="F51" t="n">
+        <v>1.7767</v>
+      </c>
+      <c r="G51" t="n">
         <v>191.2855</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>317.8124</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.8869</v>
       </c>
       <c r="F52" t="n">
+        <v>1.7662</v>
+      </c>
+      <c r="G52" t="n">
         <v>191.0158</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>315.6412</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.8692</v>
       </c>
       <c r="F53" t="n">
+        <v>1.8267</v>
+      </c>
+      <c r="G53" t="n">
         <v>210.6494</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>327.8794</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.8632</v>
       </c>
       <c r="F54" t="n">
+        <v>1.7927</v>
+      </c>
+      <c r="G54" t="n">
         <v>207.9136</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>321.0637</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.8679</v>
       </c>
       <c r="F55" t="n">
+        <v>1.7924</v>
+      </c>
+      <c r="G55" t="n">
         <v>202.971</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>320.991</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.9404</v>
       </c>
       <c r="F56" t="n">
+        <v>1.7858</v>
+      </c>
+      <c r="G56" t="n">
         <v>155.8354</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>319.6564</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.9073</v>
       </c>
       <c r="F57" t="n">
+        <v>1.7885</v>
+      </c>
+      <c r="G57" t="n">
         <v>178.3915</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>320.2063</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.8794</v>
       </c>
       <c r="F58" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="G58" t="n">
         <v>192.779</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>330.3112</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.8789</v>
       </c>
       <c r="F59" t="n">
+        <v>1.8394</v>
+      </c>
+      <c r="G59" t="n">
         <v>192.4741</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>330.3814</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.88</v>
       </c>
       <c r="F60" t="n">
+        <v>1.8408</v>
+      </c>
+      <c r="G60" t="n">
         <v>191.5402</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>330.6573</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.8802</v>
       </c>
       <c r="F61" t="n">
+        <v>1.8346</v>
+      </c>
+      <c r="G61" t="n">
         <v>190.9943</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>329.4402</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.8531</v>
       </c>
       <c r="F62" t="n">
+        <v>1.8156</v>
+      </c>
+      <c r="G62" t="n">
         <v>207.6958</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>325.6704</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.8993</v>
       </c>
       <c r="F63" t="n">
+        <v>1.8041</v>
+      </c>
+      <c r="G63" t="n">
         <v>181.7513</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>323.3533</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.8542999999999999</v>
       </c>
       <c r="F64" t="n">
+        <v>1.8093</v>
+      </c>
+      <c r="G64" t="n">
         <v>207.2294</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>324.3955</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.8941</v>
       </c>
       <c r="F65" t="n">
+        <v>1.8203</v>
+      </c>
+      <c r="G65" t="n">
         <v>183.5636</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>326.6045</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.9172</v>
       </c>
       <c r="F66" t="n">
+        <v>1.7991</v>
+      </c>
+      <c r="G66" t="n">
         <v>172.2683</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>322.355</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.9123</v>
       </c>
       <c r="F67" t="n">
+        <v>1.7768</v>
+      </c>
+      <c r="G67" t="n">
         <v>176.667</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>317.8137</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.9254</v>
       </c>
       <c r="F68" t="n">
+        <v>1.7928</v>
+      </c>
+      <c r="G68" t="n">
         <v>163.1921</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>321.0864</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="F69" t="n">
+        <v>1.2741</v>
+      </c>
+      <c r="G69" t="n">
         <v>75.047</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>188.7925</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9792</v>
       </c>
       <c r="F70" t="n">
+        <v>1.2842</v>
+      </c>
+      <c r="G70" t="n">
         <v>81.8429</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>192.2299</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9844000000000001</v>
       </c>
       <c r="F71" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="G71" t="n">
         <v>70.7718</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>188.7751</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9856</v>
       </c>
       <c r="F72" t="n">
+        <v>1.2763</v>
+      </c>
+      <c r="G72" t="n">
         <v>70.54040000000001</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>189.5521</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.9633</v>
       </c>
       <c r="F73" t="n">
+        <v>1.3268</v>
+      </c>
+      <c r="G73" t="n">
         <v>106.5844</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>206.1392</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="F74" t="n">
+        <v>1.3464</v>
+      </c>
+      <c r="G74" t="n">
         <v>85.7008</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>212.2481</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.9802999999999999</v>
       </c>
       <c r="F75" t="n">
+        <v>1.3979</v>
+      </c>
+      <c r="G75" t="n">
         <v>79.4229</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>227.4657</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.9802999999999999</v>
       </c>
       <c r="F76" t="n">
+        <v>1.3979</v>
+      </c>
+      <c r="G76" t="n">
         <v>79.4229</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>227.4657</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.9068000000000001</v>
       </c>
       <c r="F77" t="n">
+        <v>1.8148</v>
+      </c>
+      <c r="G77" t="n">
         <v>172.6373</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>325.4957</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.9087</v>
       </c>
       <c r="F78" t="n">
+        <v>1.8112</v>
+      </c>
+      <c r="G78" t="n">
         <v>171.2347</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>324.7849</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.9062</v>
       </c>
       <c r="F79" t="n">
+        <v>1.8174</v>
+      </c>
+      <c r="G79" t="n">
         <v>173.7944</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>326.0319</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.9086</v>
       </c>
       <c r="F80" t="n">
+        <v>1.8107</v>
+      </c>
+      <c r="G80" t="n">
         <v>171.2501</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>324.6752</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.9165</v>
       </c>
       <c r="F81" t="n">
+        <v>1.8028</v>
+      </c>
+      <c r="G81" t="n">
         <v>169.5574</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>323.0939</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.8595</v>
       </c>
       <c r="F82" t="n">
+        <v>1.8289</v>
+      </c>
+      <c r="G82" t="n">
         <v>206.1442</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>328.3126</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.9799</v>
       </c>
       <c r="F83" t="n">
+        <v>1.3982</v>
+      </c>
+      <c r="G83" t="n">
         <v>77.8488</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>227.5433</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.9799</v>
       </c>
       <c r="F84" t="n">
+        <v>1.3892</v>
+      </c>
+      <c r="G84" t="n">
         <v>77.5427</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>224.972</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.98</v>
       </c>
       <c r="F85" t="n">
+        <v>1.3969</v>
+      </c>
+      <c r="G85" t="n">
         <v>77.7415</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>227.1747</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9811</v>
       </c>
       <c r="F86" t="n">
+        <v>1.3165</v>
+      </c>
+      <c r="G86" t="n">
         <v>76.7372</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>202.8792</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F87" t="n">
+        <v>1.3081</v>
+      </c>
+      <c r="G87" t="n">
         <v>81.6497</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>200.1561</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.9835</v>
       </c>
       <c r="F88" t="n">
+        <v>1.3257</v>
+      </c>
+      <c r="G88" t="n">
         <v>73.44750000000001</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>205.7982</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9855</v>
       </c>
       <c r="F89" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="G89" t="n">
         <v>70.6884</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>199.1506</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.9867</v>
       </c>
       <c r="F90" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="G90" t="n">
         <v>69.5878</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>205.6845</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9863</v>
       </c>
       <c r="F91" t="n">
+        <v>1.3088</v>
+      </c>
+      <c r="G91" t="n">
         <v>69.5445</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>200.3979</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.9835</v>
       </c>
       <c r="F92" t="n">
+        <v>1.3257</v>
+      </c>
+      <c r="G92" t="n">
         <v>73.44750000000001</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>205.7982</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9863</v>
       </c>
       <c r="F93" t="n">
+        <v>1.3088</v>
+      </c>
+      <c r="G93" t="n">
         <v>69.5445</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>200.3979</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.9693000000000001</v>
       </c>
       <c r="F94" t="n">
+        <v>1.4406</v>
+      </c>
+      <c r="G94" t="n">
         <v>101.4419</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>239.3684</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.795</v>
       </c>
       <c r="F95" t="n">
+        <v>2.1076</v>
+      </c>
+      <c r="G95" t="n">
         <v>256.4459</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>379.5158</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.9694</v>
       </c>
       <c r="F96" t="n">
+        <v>1.4449</v>
+      </c>
+      <c r="G96" t="n">
         <v>101.3403</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>240.5206</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.9695</v>
       </c>
       <c r="F97" t="n">
+        <v>1.4454</v>
+      </c>
+      <c r="G97" t="n">
         <v>101.5737</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>240.6538</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.9842</v>
       </c>
       <c r="F98" t="n">
+        <v>1.3358</v>
+      </c>
+      <c r="G98" t="n">
         <v>76.3492</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>208.9743</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9823</v>
       </c>
       <c r="F99" t="n">
+        <v>1.3478</v>
+      </c>
+      <c r="G99" t="n">
         <v>79.6142</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>212.6565</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.9826</v>
       </c>
       <c r="F100" t="n">
+        <v>1.3381</v>
+      </c>
+      <c r="G100" t="n">
         <v>79.2786</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>209.6822</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.9837</v>
       </c>
       <c r="F101" t="n">
+        <v>1.3535</v>
+      </c>
+      <c r="G101" t="n">
         <v>75.9593</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>214.3939</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.9836</v>
       </c>
       <c r="F102" t="n">
+        <v>1.3576</v>
+      </c>
+      <c r="G102" t="n">
         <v>77.1332</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>215.6439</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9749</v>
       </c>
       <c r="F103" t="n">
+        <v>1.3618</v>
+      </c>
+      <c r="G103" t="n">
         <v>92.40689999999999</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>216.9149</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.982</v>
       </c>
       <c r="F104" t="n">
+        <v>1.3348</v>
+      </c>
+      <c r="G104" t="n">
         <v>79.4657</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>208.6535</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.9832</v>
       </c>
       <c r="F105" t="n">
+        <v>1.3434</v>
+      </c>
+      <c r="G105" t="n">
         <v>78.9911</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>211.321</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9827</v>
       </c>
       <c r="F106" t="n">
+        <v>1.3506</v>
+      </c>
+      <c r="G106" t="n">
         <v>78.9289</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>213.511</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9819</v>
       </c>
       <c r="F107" t="n">
+        <v>1.3484</v>
+      </c>
+      <c r="G107" t="n">
         <v>79.1541</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>212.8529</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.9837</v>
       </c>
       <c r="F108" t="n">
+        <v>1.3653</v>
+      </c>
+      <c r="G108" t="n">
         <v>80.017</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>217.9581</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.9852</v>
       </c>
       <c r="F109" t="n">
+        <v>1.3392</v>
+      </c>
+      <c r="G109" t="n">
         <v>76.0629</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>210.014</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9817</v>
       </c>
       <c r="F110" t="n">
+        <v>1.3088</v>
+      </c>
+      <c r="G110" t="n">
         <v>79.08280000000001</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>200.3983</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.9832</v>
       </c>
       <c r="F111" t="n">
+        <v>1.3213</v>
+      </c>
+      <c r="G111" t="n">
         <v>75.1728</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>204.4003</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9843</v>
       </c>
       <c r="F112" t="n">
+        <v>1.3604</v>
+      </c>
+      <c r="G112" t="n">
         <v>79.026</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>216.4683</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9858</v>
       </c>
       <c r="F113" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="G113" t="n">
         <v>75.16840000000001</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>208.4015</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9817</v>
       </c>
       <c r="F114" t="n">
+        <v>1.3093</v>
+      </c>
+      <c r="G114" t="n">
         <v>79.31789999999999</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>200.5555</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.9823</v>
       </c>
       <c r="F115" t="n">
+        <v>1.3292</v>
+      </c>
+      <c r="G115" t="n">
         <v>76.8205</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>206.9118</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.8433</v>
       </c>
       <c r="F116" t="n">
+        <v>1.8349</v>
+      </c>
+      <c r="G116" t="n">
         <v>215.4715</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>329.4887</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.8839</v>
       </c>
       <c r="F117" t="n">
+        <v>1.8447</v>
+      </c>
+      <c r="G117" t="n">
         <v>192.3805</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>331.4326</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.9832</v>
       </c>
       <c r="F118" t="n">
+        <v>1.3434</v>
+      </c>
+      <c r="G118" t="n">
         <v>78.9911</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>211.321</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.9858</v>
       </c>
       <c r="F119" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="G119" t="n">
         <v>75.16840000000001</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>208.4015</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.9491000000000001</v>
       </c>
       <c r="F120" t="n">
+        <v>1.3383</v>
+      </c>
+      <c r="G120" t="n">
         <v>116.943</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>209.7527</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.9491000000000001</v>
       </c>
       <c r="F121" t="n">
+        <v>1.3383</v>
+      </c>
+      <c r="G121" t="n">
         <v>116.943</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>209.7527</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.9853</v>
       </c>
       <c r="F122" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G122" t="n">
         <v>67.282</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>183.8576</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9858</v>
       </c>
       <c r="F123" t="n">
+        <v>1.3356</v>
+      </c>
+      <c r="G123" t="n">
         <v>75.6384</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>208.9034</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9865</v>
       </c>
       <c r="F124" t="n">
+        <v>1.3367</v>
+      </c>
+      <c r="G124" t="n">
         <v>74.0454</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>209.2376</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="F125" t="n">
+        <v>1.4459</v>
+      </c>
+      <c r="G125" t="n">
         <v>100.2053</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>240.7978</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.9786</v>
       </c>
       <c r="F126" t="n">
+        <v>1.3049</v>
+      </c>
+      <c r="G126" t="n">
         <v>81.2277</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>199.1046</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.7876</v>
       </c>
       <c r="F127" t="n">
+        <v>1.9611</v>
+      </c>
+      <c r="G127" t="n">
         <v>238.9323</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>353.5263</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.9774</v>
       </c>
       <c r="F128" t="n">
+        <v>1.3082</v>
+      </c>
+      <c r="G128" t="n">
         <v>82.5391</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>200.1882</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="F129" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="G129" t="n">
         <v>82.48269999999999</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>200.1315</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.9771</v>
       </c>
       <c r="F130" t="n">
+        <v>1.3122</v>
+      </c>
+      <c r="G130" t="n">
         <v>83.0489</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>201.4761</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.9772</v>
       </c>
       <c r="F131" t="n">
+        <v>1.3096</v>
+      </c>
+      <c r="G131" t="n">
         <v>82.77419999999999</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>200.6486</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.9848</v>
       </c>
       <c r="F132" t="n">
+        <v>1.3007</v>
+      </c>
+      <c r="G132" t="n">
         <v>70.19029999999999</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>197.731</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.9835</v>
       </c>
       <c r="F133" t="n">
+        <v>1.3057</v>
+      </c>
+      <c r="G133" t="n">
         <v>71.7961</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>199.3757</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.9779</v>
       </c>
       <c r="F134" t="n">
+        <v>1.3066</v>
+      </c>
+      <c r="G134" t="n">
         <v>81.6867</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>199.6845</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.9776</v>
       </c>
       <c r="F135" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="G135" t="n">
         <v>82.2086</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>200.1325</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.9774</v>
       </c>
       <c r="F136" t="n">
+        <v>1.3086</v>
+      </c>
+      <c r="G136" t="n">
         <v>82.4747</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>200.3094</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9791</v>
       </c>
       <c r="F137" t="n">
+        <v>1.3036</v>
+      </c>
+      <c r="G137" t="n">
         <v>80.8704</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>198.7059</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9861</v>
       </c>
       <c r="F138" t="n">
+        <v>1.3068</v>
+      </c>
+      <c r="G138" t="n">
         <v>68.3527</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>199.7458</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9862</v>
       </c>
       <c r="F139" t="n">
+        <v>1.3082</v>
+      </c>
+      <c r="G139" t="n">
         <v>68.35290000000001</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>200.1827</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.9804</v>
       </c>
       <c r="F140" t="n">
+        <v>1.2963</v>
+      </c>
+      <c r="G140" t="n">
         <v>81.4551</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>196.2966</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9801</v>
       </c>
       <c r="F141" t="n">
+        <v>1.2908</v>
+      </c>
+      <c r="G141" t="n">
         <v>81.9294</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>194.4432</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9861</v>
       </c>
       <c r="F142" t="n">
+        <v>1.3068</v>
+      </c>
+      <c r="G142" t="n">
         <v>68.3527</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>199.7458</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9863</v>
       </c>
       <c r="F143" t="n">
+        <v>1.3039</v>
+      </c>
+      <c r="G143" t="n">
         <v>67.7602</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>198.7855</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9849</v>
       </c>
       <c r="F144" t="n">
+        <v>1.2986</v>
+      </c>
+      <c r="G144" t="n">
         <v>70.9256</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>197.0597</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9801</v>
       </c>
       <c r="F145" t="n">
+        <v>1.2908</v>
+      </c>
+      <c r="G145" t="n">
         <v>81.9294</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>194.4432</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.7882</v>
       </c>
       <c r="F146" t="n">
+        <v>1.9624</v>
+      </c>
+      <c r="G146" t="n">
         <v>238.3036</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>353.7653</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.79</v>
       </c>
       <c r="F147" t="n">
+        <v>1.9612</v>
+      </c>
+      <c r="G147" t="n">
         <v>237.7503</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>353.5388</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.7895</v>
       </c>
       <c r="F148" t="n">
+        <v>1.9593</v>
+      </c>
+      <c r="G148" t="n">
         <v>238.2072</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>353.1922</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.7907</v>
       </c>
       <c r="F149" t="n">
+        <v>1.9592</v>
+      </c>
+      <c r="G149" t="n">
         <v>237.7169</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>353.1731</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.7887999999999999</v>
       </c>
       <c r="F150" t="n">
+        <v>1.9624</v>
+      </c>
+      <c r="G150" t="n">
         <v>238.3628</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>353.7547</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.7887999999999999</v>
       </c>
       <c r="F151" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="G151" t="n">
         <v>238.3192</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>353.8684</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.7896</v>
       </c>
       <c r="F152" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="G152" t="n">
         <v>237.8898</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>353.8741</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.7903</v>
       </c>
       <c r="F153" t="n">
+        <v>1.9621</v>
+      </c>
+      <c r="G153" t="n">
         <v>237.6603</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>353.7078</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.7891</v>
       </c>
       <c r="F154" t="n">
+        <v>1.9547</v>
+      </c>
+      <c r="G154" t="n">
         <v>238.2105</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>352.337</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.9042</v>
       </c>
       <c r="F155" t="n">
+        <v>1.7918</v>
+      </c>
+      <c r="G155" t="n">
         <v>179.1117</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>320.8706</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.9102</v>
       </c>
       <c r="F156" t="n">
+        <v>1.8025</v>
+      </c>
+      <c r="G156" t="n">
         <v>172.9713</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>323.0295</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.9063</v>
       </c>
       <c r="F157" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="G157" t="n">
         <v>175.1256</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>324.9524</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.878</v>
       </c>
       <c r="F158" t="n">
+        <v>1.8083</v>
+      </c>
+      <c r="G158" t="n">
         <v>200.4145</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>324.2083</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.986</v>
       </c>
       <c r="F159" t="n">
+        <v>1.2784</v>
+      </c>
+      <c r="G159" t="n">
         <v>67.0766</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>190.2741</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.8735000000000001</v>
       </c>
       <c r="F160" t="n">
+        <v>1.8847</v>
+      </c>
+      <c r="G160" t="n">
         <v>197.9142</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>339.1699</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.8729</v>
       </c>
       <c r="F161" t="n">
+        <v>1.8953</v>
+      </c>
+      <c r="G161" t="n">
         <v>198.1167</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>341.2114</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.9782</v>
       </c>
       <c r="F162" t="n">
+        <v>1.2699</v>
+      </c>
+      <c r="G162" t="n">
         <v>81.43689999999999</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>187.3425</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9808</v>
       </c>
       <c r="F163" t="n">
+        <v>1.2896</v>
+      </c>
+      <c r="G163" t="n">
         <v>78.1712</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>194.0708</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9804</v>
       </c>
       <c r="F164" t="n">
+        <v>1.2964</v>
+      </c>
+      <c r="G164" t="n">
         <v>81.45780000000001</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>196.3186</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="F165" t="n">
+        <v>1.4459</v>
+      </c>
+      <c r="G165" t="n">
         <v>100.2053</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>240.7978</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.7937</v>
       </c>
       <c r="F166" t="n">
+        <v>2.1058</v>
+      </c>
+      <c r="G166" t="n">
         <v>256.5079</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>379.2027</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.9771</v>
       </c>
       <c r="F167" t="n">
+        <v>1.3092</v>
+      </c>
+      <c r="G167" t="n">
         <v>83.23520000000001</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>200.5324</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9869</v>
       </c>
       <c r="F168" t="n">
+        <v>1.2875</v>
+      </c>
+      <c r="G168" t="n">
         <v>67.7345</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>193.3371</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.9856</v>
       </c>
       <c r="F169" t="n">
+        <v>1.3238</v>
+      </c>
+      <c r="G169" t="n">
         <v>70.9252</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>205.1854</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.9791</v>
       </c>
       <c r="F170" t="n">
+        <v>1.3555</v>
+      </c>
+      <c r="G170" t="n">
         <v>86.00060000000001</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>215.0183</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9836</v>
       </c>
       <c r="F171" t="n">
+        <v>1.3424</v>
+      </c>
+      <c r="G171" t="n">
         <v>74.48860000000001</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>211.0028</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9851</v>
       </c>
       <c r="F172" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="G172" t="n">
         <v>69.51220000000001</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>196.1808</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.beta.carotene/RANDOMSEARCH_DETAILS_trans.beta.carotene.xlsx
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9855</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3182</v>
+        <v>0.6998</v>
       </c>
       <c r="G2" t="n">
-        <v>70.33839999999999</v>
+        <v>74.1867</v>
       </c>
       <c r="H2" t="n">
-        <v>203.4208</v>
+        <v>192.4358</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9811</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2966</v>
+        <v>0.7047</v>
       </c>
       <c r="G3" t="n">
-        <v>71.1319</v>
+        <v>77.0107</v>
       </c>
       <c r="H3" t="n">
-        <v>196.3833</v>
+        <v>190.8648</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9421</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4406</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>101.4419</v>
+        <v>126.1691</v>
       </c>
       <c r="H4" t="n">
-        <v>239.3684</v>
+        <v>233.2529</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8773</v>
+        <v>0.8035</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8542</v>
+        <v>0.0208</v>
       </c>
       <c r="G5" t="n">
-        <v>192.7845</v>
+        <v>228.1077</v>
       </c>
       <c r="H5" t="n">
-        <v>333.2888</v>
+        <v>347.5733</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8784</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8326</v>
+        <v>0.0384</v>
       </c>
       <c r="G6" t="n">
-        <v>193.1334</v>
+        <v>229.9218</v>
       </c>
       <c r="H6" t="n">
-        <v>329.036</v>
+        <v>344.4263</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9548</v>
+        <v>0.9439</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3154</v>
+        <v>0.6142</v>
       </c>
       <c r="G7" t="n">
-        <v>110.5537</v>
+        <v>118.2409</v>
       </c>
       <c r="H7" t="n">
-        <v>202.5303</v>
+        <v>218.1539</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9699</v>
+        <v>0.9729</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3726</v>
+        <v>0.6291</v>
       </c>
       <c r="G8" t="n">
-        <v>95.04349999999999</v>
+        <v>86.9267</v>
       </c>
       <c r="H8" t="n">
-        <v>220.1135</v>
+        <v>213.9166</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9847</v>
+        <v>0.9655</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3253</v>
+        <v>0.6956</v>
       </c>
       <c r="G9" t="n">
-        <v>70.54770000000001</v>
+        <v>98.22620000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>205.6857</v>
+        <v>193.7749</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9695</v>
+        <v>0.9727</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3746</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>95.45740000000001</v>
+        <v>87.1438</v>
       </c>
       <c r="H10" t="n">
-        <v>220.7184</v>
+        <v>213.4998</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9689</v>
+        <v>0.9718</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3724</v>
+        <v>0.6259</v>
       </c>
       <c r="G11" t="n">
-        <v>95.9791</v>
+        <v>88.12009999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>220.0607</v>
+        <v>214.8345</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9675</v>
+        <v>0.9679</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3712</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>97.7591</v>
+        <v>92.2914</v>
       </c>
       <c r="H12" t="n">
-        <v>219.6967</v>
+        <v>213.4905</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9677</v>
+        <v>0.9688</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3676</v>
+        <v>0.6364</v>
       </c>
       <c r="G13" t="n">
-        <v>98.13630000000001</v>
+        <v>91.1605</v>
       </c>
       <c r="H13" t="n">
-        <v>218.6378</v>
+        <v>211.8057</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.969</v>
+        <v>0.9719</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3735</v>
+        <v>0.6268</v>
       </c>
       <c r="G14" t="n">
-        <v>96.0475</v>
+        <v>87.94670000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>220.3833</v>
+        <v>214.5814</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9678</v>
+        <v>0.9718</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3721</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>97.2657</v>
+        <v>88.1632</v>
       </c>
       <c r="H15" t="n">
-        <v>219.9646</v>
+        <v>213.7816</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9794</v>
+        <v>0.9718</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3725</v>
+        <v>0.6279</v>
       </c>
       <c r="G16" t="n">
-        <v>79.8015</v>
+        <v>88.3091</v>
       </c>
       <c r="H16" t="n">
-        <v>220.093</v>
+        <v>214.2477</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9678</v>
+        <v>0.9688</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3636</v>
+        <v>0.6338</v>
       </c>
       <c r="G17" t="n">
-        <v>98.0651</v>
+        <v>91.0609</v>
       </c>
       <c r="H17" t="n">
-        <v>217.4327</v>
+        <v>212.5364</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9848</v>
+        <v>0.9651</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3182</v>
+        <v>0.6988</v>
       </c>
       <c r="G18" t="n">
-        <v>69.6554</v>
+        <v>99.0433</v>
       </c>
       <c r="H18" t="n">
-        <v>203.4128</v>
+        <v>192.766</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9842</v>
+        <v>0.9624</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3184</v>
+        <v>0.6899</v>
       </c>
       <c r="G19" t="n">
-        <v>71.7522</v>
+        <v>101.7011</v>
       </c>
       <c r="H19" t="n">
-        <v>203.4712</v>
+        <v>195.5975</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9768</v>
+        <v>0.9618</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3248</v>
+        <v>0.6871</v>
       </c>
       <c r="G20" t="n">
-        <v>87.848</v>
+        <v>102.4174</v>
       </c>
       <c r="H20" t="n">
-        <v>205.5041</v>
+        <v>196.4596</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9769</v>
+        <v>0.9625</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3236</v>
+        <v>0.6911</v>
       </c>
       <c r="G21" t="n">
-        <v>88.27070000000001</v>
+        <v>101.9583</v>
       </c>
       <c r="H21" t="n">
-        <v>205.1437</v>
+        <v>195.2123</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9811</v>
+        <v>0.9611</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3238</v>
+        <v>0.6905</v>
       </c>
       <c r="G22" t="n">
-        <v>77.0121</v>
+        <v>103.1646</v>
       </c>
       <c r="H22" t="n">
-        <v>205.1959</v>
+        <v>195.389</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9853</v>
+        <v>0.9596</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3131</v>
+        <v>0.6914</v>
       </c>
       <c r="G23" t="n">
-        <v>73.16719999999999</v>
+        <v>104.5014</v>
       </c>
       <c r="H23" t="n">
-        <v>201.7618</v>
+        <v>195.1169</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9852</v>
+        <v>0.9595</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3148</v>
+        <v>0.6911</v>
       </c>
       <c r="G24" t="n">
-        <v>71.9623</v>
+        <v>104.8892</v>
       </c>
       <c r="H24" t="n">
-        <v>202.3404</v>
+        <v>195.2158</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9868</v>
+        <v>0.9591</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3223</v>
+        <v>0.6917</v>
       </c>
       <c r="G25" t="n">
-        <v>65.9478</v>
+        <v>105.3154</v>
       </c>
       <c r="H25" t="n">
-        <v>204.7296</v>
+        <v>195.0329</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9797</v>
+        <v>0.9684</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3154</v>
+        <v>0.707</v>
       </c>
       <c r="G26" t="n">
-        <v>78.37909999999999</v>
+        <v>94.9881</v>
       </c>
       <c r="H26" t="n">
-        <v>202.5314</v>
+        <v>190.1353</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9861</v>
+        <v>0.965</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3228</v>
+        <v>0.6939</v>
       </c>
       <c r="G27" t="n">
-        <v>66.93210000000001</v>
+        <v>99.015</v>
       </c>
       <c r="H27" t="n">
-        <v>204.8939</v>
+        <v>194.3322</v>
       </c>
     </row>
     <row r="28">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9805</v>
+        <v>0.9766</v>
       </c>
       <c r="F28" t="n">
-        <v>1.314</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>77.9609</v>
+        <v>80.8614</v>
       </c>
       <c r="H28" t="n">
-        <v>202.0641</v>
+        <v>193.2943</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9861</v>
+        <v>0.963</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3245</v>
+        <v>0.6887</v>
       </c>
       <c r="G29" t="n">
-        <v>71.4833</v>
+        <v>101.4773</v>
       </c>
       <c r="H29" t="n">
-        <v>205.4297</v>
+        <v>195.9546</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9856</v>
+        <v>0.9623</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3216</v>
+        <v>0.6902</v>
       </c>
       <c r="G30" t="n">
-        <v>71.801</v>
+        <v>101.7544</v>
       </c>
       <c r="H30" t="n">
-        <v>204.4992</v>
+        <v>195.5043</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9866</v>
+        <v>0.9615</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3152</v>
+        <v>0.6816</v>
       </c>
       <c r="G31" t="n">
-        <v>69.00620000000001</v>
+        <v>102.9626</v>
       </c>
       <c r="H31" t="n">
-        <v>202.4475</v>
+        <v>198.1799</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9799</v>
+        <v>0.9776</v>
       </c>
       <c r="F32" t="n">
-        <v>1.327</v>
+        <v>0.6796</v>
       </c>
       <c r="G32" t="n">
-        <v>81.27760000000001</v>
+        <v>80.4329</v>
       </c>
       <c r="H32" t="n">
-        <v>206.2081</v>
+        <v>198.8041</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9856</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3259</v>
+        <v>0.6838</v>
       </c>
       <c r="G33" t="n">
-        <v>70.83750000000001</v>
+        <v>102.8721</v>
       </c>
       <c r="H33" t="n">
-        <v>205.8494</v>
+        <v>197.5169</v>
       </c>
     </row>
     <row r="34">
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9818</v>
+        <v>0.978</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3227</v>
+        <v>0.6785</v>
       </c>
       <c r="G34" t="n">
-        <v>78.1093</v>
+        <v>80.9813</v>
       </c>
       <c r="H34" t="n">
-        <v>204.8343</v>
+        <v>199.1418</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9855</v>
+        <v>0.9796</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3155</v>
+        <v>0.6886</v>
       </c>
       <c r="G35" t="n">
-        <v>67.77549999999999</v>
+        <v>78.7649</v>
       </c>
       <c r="H35" t="n">
-        <v>202.5374</v>
+        <v>195.9913</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9866</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3261</v>
+        <v>0.6923</v>
       </c>
       <c r="G36" t="n">
-        <v>69.6146</v>
+        <v>98.4939</v>
       </c>
       <c r="H36" t="n">
-        <v>205.9353</v>
+        <v>194.8356</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9866</v>
+        <v>0.9754</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3078</v>
+        <v>0.7084</v>
       </c>
       <c r="G37" t="n">
-        <v>69.27379999999999</v>
+        <v>82.0882</v>
       </c>
       <c r="H37" t="n">
-        <v>200.0682</v>
+        <v>189.6564</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9676</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3052</v>
+        <v>0.7168</v>
       </c>
       <c r="G38" t="n">
-        <v>67.40949999999999</v>
+        <v>96.1247</v>
       </c>
       <c r="H38" t="n">
-        <v>199.2216</v>
+        <v>186.9007</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9797</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3138</v>
+        <v>0.7166</v>
       </c>
       <c r="G39" t="n">
-        <v>81.07810000000001</v>
+        <v>97.4243</v>
       </c>
       <c r="H39" t="n">
-        <v>202.0184</v>
+        <v>186.9851</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9787</v>
+        <v>0.9778</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3095</v>
+        <v>0.7109</v>
       </c>
       <c r="G40" t="n">
-        <v>83.6001</v>
+        <v>80.12779999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>200.601</v>
+        <v>188.8429</v>
       </c>
     </row>
     <row r="41">
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.982</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>1.32</v>
+        <v>0.6818</v>
       </c>
       <c r="G41" t="n">
-        <v>77.7141</v>
+        <v>80.2642</v>
       </c>
       <c r="H41" t="n">
-        <v>203.9835</v>
+        <v>198.1201</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9856</v>
+        <v>0.9794</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3175</v>
+        <v>0.6901</v>
       </c>
       <c r="G42" t="n">
-        <v>68.2711</v>
+        <v>78.9512</v>
       </c>
       <c r="H42" t="n">
-        <v>203.189</v>
+        <v>195.5156</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9866</v>
+        <v>0.9801</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3253</v>
+        <v>0.6916</v>
       </c>
       <c r="G43" t="n">
-        <v>69.6247</v>
+        <v>75.6401</v>
       </c>
       <c r="H43" t="n">
-        <v>205.6807</v>
+        <v>195.0621</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3089</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>69.5001</v>
+        <v>82.26220000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>200.4156</v>
+        <v>190.4001</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9875</v>
+        <v>0.9675</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3047</v>
+        <v>0.7159</v>
       </c>
       <c r="G45" t="n">
-        <v>67.37430000000001</v>
+        <v>96.2901</v>
       </c>
       <c r="H45" t="n">
-        <v>199.038</v>
+        <v>187.2158</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9801</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>1.3171</v>
+        <v>0.717</v>
       </c>
       <c r="G46" t="n">
-        <v>80.1495</v>
+        <v>97.4714</v>
       </c>
       <c r="H46" t="n">
-        <v>203.0775</v>
+        <v>186.8559</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3106</v>
+        <v>0.7116</v>
       </c>
       <c r="G47" t="n">
-        <v>83.2957</v>
+        <v>80.3366</v>
       </c>
       <c r="H47" t="n">
-        <v>200.9857</v>
+        <v>188.6338</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9866</v>
+        <v>0.9769</v>
       </c>
       <c r="F48" t="n">
-        <v>1.3308</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>70.6643</v>
+        <v>82.10120000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>207.4157</v>
+        <v>192.6663</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9867</v>
+        <v>0.9648</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3253</v>
+        <v>0.6977</v>
       </c>
       <c r="G49" t="n">
-        <v>70.53279999999999</v>
+        <v>98.7364</v>
       </c>
       <c r="H49" t="n">
-        <v>205.6672</v>
+        <v>193.1212</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9147</v>
+        <v>0.8701</v>
       </c>
       <c r="F50" t="n">
-        <v>1.8263</v>
+        <v>0.1462</v>
       </c>
       <c r="G50" t="n">
-        <v>172.0859</v>
+        <v>200.547</v>
       </c>
       <c r="H50" t="n">
-        <v>327.7899</v>
+        <v>324.5425</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.891</v>
+        <v>0.8575</v>
       </c>
       <c r="F51" t="n">
-        <v>1.7767</v>
+        <v>0.1578</v>
       </c>
       <c r="G51" t="n">
-        <v>191.2855</v>
+        <v>210.4879</v>
       </c>
       <c r="H51" t="n">
-        <v>317.8124</v>
+        <v>322.3404</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8869</v>
+        <v>0.8577</v>
       </c>
       <c r="F52" t="n">
-        <v>1.7662</v>
+        <v>0.1579</v>
       </c>
       <c r="G52" t="n">
-        <v>191.0158</v>
+        <v>210.8516</v>
       </c>
       <c r="H52" t="n">
-        <v>315.6412</v>
+        <v>322.3246</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8692</v>
+        <v>0.8851</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8267</v>
+        <v>0.1629</v>
       </c>
       <c r="G53" t="n">
-        <v>210.6494</v>
+        <v>197.3504</v>
       </c>
       <c r="H53" t="n">
-        <v>327.8794</v>
+        <v>321.3666</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8632</v>
+        <v>0.8943</v>
       </c>
       <c r="F54" t="n">
-        <v>1.7927</v>
+        <v>0.1818</v>
       </c>
       <c r="G54" t="n">
-        <v>207.9136</v>
+        <v>182.2662</v>
       </c>
       <c r="H54" t="n">
-        <v>321.0637</v>
+        <v>317.711</v>
       </c>
     </row>
     <row r="55">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8679</v>
+        <v>0.8577</v>
       </c>
       <c r="F55" t="n">
-        <v>1.7924</v>
+        <v>0.098</v>
       </c>
       <c r="G55" t="n">
-        <v>202.971</v>
+        <v>206.6015</v>
       </c>
       <c r="H55" t="n">
-        <v>320.991</v>
+        <v>333.5786</v>
       </c>
     </row>
     <row r="56">
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9404</v>
+        <v>0.9405</v>
       </c>
       <c r="F56" t="n">
-        <v>1.7858</v>
+        <v>0.1469</v>
       </c>
       <c r="G56" t="n">
-        <v>155.8354</v>
+        <v>154.4891</v>
       </c>
       <c r="H56" t="n">
-        <v>319.6564</v>
+        <v>324.4217</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9073</v>
+        <v>0.971</v>
       </c>
       <c r="F57" t="n">
-        <v>1.7885</v>
+        <v>0.1586</v>
       </c>
       <c r="G57" t="n">
-        <v>178.3915</v>
+        <v>113.6301</v>
       </c>
       <c r="H57" t="n">
-        <v>320.2063</v>
+        <v>322.1766</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8794</v>
+        <v>0.7994</v>
       </c>
       <c r="F58" t="n">
-        <v>1.839</v>
+        <v>0.0387</v>
       </c>
       <c r="G58" t="n">
-        <v>192.779</v>
+        <v>229.8061</v>
       </c>
       <c r="H58" t="n">
-        <v>330.3112</v>
+        <v>344.3802</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8789</v>
+        <v>0.7996</v>
       </c>
       <c r="F59" t="n">
-        <v>1.8394</v>
+        <v>0.0394</v>
       </c>
       <c r="G59" t="n">
-        <v>192.4741</v>
+        <v>229.5539</v>
       </c>
       <c r="H59" t="n">
-        <v>330.3814</v>
+        <v>344.2465</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.88</v>
+        <v>0.8002</v>
       </c>
       <c r="F60" t="n">
-        <v>1.8408</v>
+        <v>0.0385</v>
       </c>
       <c r="G60" t="n">
-        <v>191.5402</v>
+        <v>229.3551</v>
       </c>
       <c r="H60" t="n">
-        <v>330.6573</v>
+        <v>344.4164</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8802</v>
+        <v>0.8013</v>
       </c>
       <c r="F61" t="n">
-        <v>1.8346</v>
+        <v>0.0376</v>
       </c>
       <c r="G61" t="n">
-        <v>190.9943</v>
+        <v>228.8713</v>
       </c>
       <c r="H61" t="n">
-        <v>329.4402</v>
+        <v>344.5725</v>
       </c>
     </row>
     <row r="62">
@@ -2398,16 +2398,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8531</v>
+        <v>0.8479</v>
       </c>
       <c r="F62" t="n">
-        <v>1.8156</v>
+        <v>0.1068</v>
       </c>
       <c r="G62" t="n">
-        <v>207.6958</v>
+        <v>206.9955</v>
       </c>
       <c r="H62" t="n">
-        <v>325.6704</v>
+        <v>331.9598</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8993</v>
+        <v>0.8699</v>
       </c>
       <c r="F63" t="n">
-        <v>1.8041</v>
+        <v>0.1103</v>
       </c>
       <c r="G63" t="n">
-        <v>181.7513</v>
+        <v>192.8149</v>
       </c>
       <c r="H63" t="n">
-        <v>323.3533</v>
+        <v>331.2925</v>
       </c>
     </row>
     <row r="64">
@@ -2462,16 +2462,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.8431</v>
       </c>
       <c r="F64" t="n">
-        <v>1.8093</v>
+        <v>0.1078</v>
       </c>
       <c r="G64" t="n">
-        <v>207.2294</v>
+        <v>208.4783</v>
       </c>
       <c r="H64" t="n">
-        <v>324.3955</v>
+        <v>331.7733</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8941</v>
+        <v>0.8468</v>
       </c>
       <c r="F65" t="n">
-        <v>1.8203</v>
+        <v>0.0948</v>
       </c>
       <c r="G65" t="n">
-        <v>183.5636</v>
+        <v>207.4311</v>
       </c>
       <c r="H65" t="n">
-        <v>326.6045</v>
+        <v>334.1651</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9172</v>
+        <v>0.8685</v>
       </c>
       <c r="F66" t="n">
-        <v>1.7991</v>
+        <v>0.1327</v>
       </c>
       <c r="G66" t="n">
-        <v>172.2683</v>
+        <v>203.5041</v>
       </c>
       <c r="H66" t="n">
-        <v>322.355</v>
+        <v>327.1089</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9123</v>
+        <v>0.9267</v>
       </c>
       <c r="F67" t="n">
-        <v>1.7768</v>
+        <v>0.1425</v>
       </c>
       <c r="G67" t="n">
-        <v>176.667</v>
+        <v>161.0821</v>
       </c>
       <c r="H67" t="n">
-        <v>317.8137</v>
+        <v>325.2443</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9254</v>
+        <v>0.9049</v>
       </c>
       <c r="F68" t="n">
-        <v>1.7928</v>
+        <v>0.1482</v>
       </c>
       <c r="G68" t="n">
-        <v>163.1921</v>
+        <v>177.4922</v>
       </c>
       <c r="H68" t="n">
-        <v>321.0864</v>
+        <v>324.1651</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9776</v>
       </c>
       <c r="F69" t="n">
-        <v>1.2741</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>75.047</v>
+        <v>80.8526</v>
       </c>
       <c r="H69" t="n">
-        <v>188.7925</v>
+        <v>186.44</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9792</v>
+        <v>0.976</v>
       </c>
       <c r="F70" t="n">
-        <v>1.2842</v>
+        <v>0.6979</v>
       </c>
       <c r="G70" t="n">
-        <v>81.8429</v>
+        <v>83.77</v>
       </c>
       <c r="H70" t="n">
-        <v>192.2299</v>
+        <v>193.0663</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9798</v>
       </c>
       <c r="F71" t="n">
-        <v>1.274</v>
+        <v>0.7091</v>
       </c>
       <c r="G71" t="n">
-        <v>70.7718</v>
+        <v>77.6447</v>
       </c>
       <c r="H71" t="n">
-        <v>188.7751</v>
+        <v>189.4534</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9856</v>
+        <v>0.9767</v>
       </c>
       <c r="F72" t="n">
-        <v>1.2763</v>
+        <v>0.7091</v>
       </c>
       <c r="G72" t="n">
-        <v>70.54040000000001</v>
+        <v>80.84529999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>189.5521</v>
+        <v>189.4508</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9633</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>1.3268</v>
+        <v>0.6671</v>
       </c>
       <c r="G73" t="n">
-        <v>106.5844</v>
+        <v>85.0611</v>
       </c>
       <c r="H73" t="n">
-        <v>206.1392</v>
+        <v>202.6571</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>0.9772999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>1.3464</v>
+        <v>0.6587</v>
       </c>
       <c r="G74" t="n">
-        <v>85.7008</v>
+        <v>83.68510000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>212.2481</v>
+        <v>205.1851</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9472</v>
       </c>
       <c r="F75" t="n">
-        <v>1.3979</v>
+        <v>0.6389</v>
       </c>
       <c r="G75" t="n">
-        <v>79.4229</v>
+        <v>117.8004</v>
       </c>
       <c r="H75" t="n">
-        <v>227.4657</v>
+        <v>211.0516</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9472</v>
       </c>
       <c r="F76" t="n">
-        <v>1.3979</v>
+        <v>0.6389</v>
       </c>
       <c r="G76" t="n">
-        <v>79.4229</v>
+        <v>117.8004</v>
       </c>
       <c r="H76" t="n">
-        <v>227.4657</v>
+        <v>211.0516</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.8275</v>
       </c>
       <c r="F77" t="n">
-        <v>1.8148</v>
+        <v>0.0536</v>
       </c>
       <c r="G77" t="n">
-        <v>172.6373</v>
+        <v>215.9517</v>
       </c>
       <c r="H77" t="n">
-        <v>325.4957</v>
+        <v>341.6976</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9087</v>
+        <v>0.8104</v>
       </c>
       <c r="F78" t="n">
-        <v>1.8112</v>
+        <v>0.0517</v>
       </c>
       <c r="G78" t="n">
-        <v>171.2347</v>
+        <v>223.6842</v>
       </c>
       <c r="H78" t="n">
-        <v>324.7849</v>
+        <v>342.0346</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9062</v>
+        <v>0.8101</v>
       </c>
       <c r="F79" t="n">
-        <v>1.8174</v>
+        <v>0.0518</v>
       </c>
       <c r="G79" t="n">
-        <v>173.7944</v>
+        <v>223.7905</v>
       </c>
       <c r="H79" t="n">
-        <v>326.0319</v>
+        <v>342.0181</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9086</v>
+        <v>0.8104</v>
       </c>
       <c r="F80" t="n">
-        <v>1.8107</v>
+        <v>0.0525</v>
       </c>
       <c r="G80" t="n">
-        <v>171.2501</v>
+        <v>223.7074</v>
       </c>
       <c r="H80" t="n">
-        <v>324.6752</v>
+        <v>341.8861</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9165</v>
+        <v>0.89</v>
       </c>
       <c r="F81" t="n">
-        <v>1.8028</v>
+        <v>0.0765</v>
       </c>
       <c r="G81" t="n">
-        <v>169.5574</v>
+        <v>185.4986</v>
       </c>
       <c r="H81" t="n">
-        <v>323.0939</v>
+        <v>337.5368</v>
       </c>
     </row>
     <row r="82">
@@ -3038,16 +3038,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8595</v>
+        <v>0.8446</v>
       </c>
       <c r="F82" t="n">
-        <v>1.8289</v>
+        <v>0.0674</v>
       </c>
       <c r="G82" t="n">
-        <v>206.1442</v>
+        <v>210.6247</v>
       </c>
       <c r="H82" t="n">
-        <v>328.3126</v>
+        <v>339.1911</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9799</v>
+        <v>0.947</v>
       </c>
       <c r="F83" t="n">
-        <v>1.3982</v>
+        <v>0.6395</v>
       </c>
       <c r="G83" t="n">
-        <v>77.8488</v>
+        <v>117.9821</v>
       </c>
       <c r="H83" t="n">
-        <v>227.5433</v>
+        <v>210.8934</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9799</v>
+        <v>0.9469</v>
       </c>
       <c r="F84" t="n">
-        <v>1.3892</v>
+        <v>0.6399</v>
       </c>
       <c r="G84" t="n">
-        <v>77.5427</v>
+        <v>118.075</v>
       </c>
       <c r="H84" t="n">
-        <v>224.972</v>
+        <v>210.7686</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.98</v>
+        <v>0.9466</v>
       </c>
       <c r="F85" t="n">
-        <v>1.3969</v>
+        <v>0.6367</v>
       </c>
       <c r="G85" t="n">
-        <v>77.7415</v>
+        <v>118.377</v>
       </c>
       <c r="H85" t="n">
-        <v>227.1747</v>
+        <v>211.7146</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9811</v>
+        <v>0.9655</v>
       </c>
       <c r="F86" t="n">
-        <v>1.3165</v>
+        <v>0.6712</v>
       </c>
       <c r="G86" t="n">
-        <v>76.7372</v>
+        <v>98.17570000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>202.8792</v>
+        <v>201.403</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9651</v>
       </c>
       <c r="F87" t="n">
-        <v>1.3081</v>
+        <v>0.6733</v>
       </c>
       <c r="G87" t="n">
-        <v>81.6497</v>
+        <v>98.9936</v>
       </c>
       <c r="H87" t="n">
-        <v>200.1561</v>
+        <v>200.7496</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9835</v>
+        <v>0.9608</v>
       </c>
       <c r="F88" t="n">
-        <v>1.3257</v>
+        <v>0.677</v>
       </c>
       <c r="G88" t="n">
-        <v>73.44750000000001</v>
+        <v>104.2362</v>
       </c>
       <c r="H88" t="n">
-        <v>205.7982</v>
+        <v>199.6251</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9855</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>1.305</v>
+        <v>0.6737</v>
       </c>
       <c r="G89" t="n">
-        <v>70.6884</v>
+        <v>80.8193</v>
       </c>
       <c r="H89" t="n">
-        <v>199.1506</v>
+        <v>200.6258</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9867</v>
+        <v>0.9801</v>
       </c>
       <c r="F90" t="n">
-        <v>1.3253</v>
+        <v>0.6918</v>
       </c>
       <c r="G90" t="n">
-        <v>69.5878</v>
+        <v>75.5412</v>
       </c>
       <c r="H90" t="n">
-        <v>205.6845</v>
+        <v>194.9968</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9863</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>1.3088</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="G91" t="n">
-        <v>69.5445</v>
+        <v>82.26220000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>200.3979</v>
+        <v>190.3991</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9835</v>
+        <v>0.9608</v>
       </c>
       <c r="F92" t="n">
-        <v>1.3257</v>
+        <v>0.677</v>
       </c>
       <c r="G92" t="n">
-        <v>73.44750000000001</v>
+        <v>104.2362</v>
       </c>
       <c r="H92" t="n">
-        <v>205.7982</v>
+        <v>199.6251</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9863</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>1.3088</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>69.5445</v>
+        <v>82.26220000000001</v>
       </c>
       <c r="H93" t="n">
-        <v>200.3979</v>
+        <v>190.3991</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9421</v>
       </c>
       <c r="F94" t="n">
-        <v>1.4406</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>101.4419</v>
+        <v>126.1691</v>
       </c>
       <c r="H94" t="n">
-        <v>239.3684</v>
+        <v>233.2529</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.795</v>
+        <v>0.8205</v>
       </c>
       <c r="F95" t="n">
-        <v>2.1076</v>
+        <v>-0.0871</v>
       </c>
       <c r="G95" t="n">
-        <v>256.4459</v>
+        <v>232.5961</v>
       </c>
       <c r="H95" t="n">
-        <v>379.5158</v>
+        <v>366.2165</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9694</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>1.4449</v>
+        <v>0.5595</v>
       </c>
       <c r="G96" t="n">
-        <v>101.3403</v>
+        <v>126.2522</v>
       </c>
       <c r="H96" t="n">
-        <v>240.5206</v>
+        <v>233.122</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9695</v>
+        <v>0.9418</v>
       </c>
       <c r="F97" t="n">
-        <v>1.4454</v>
+        <v>0.5602</v>
       </c>
       <c r="G97" t="n">
-        <v>101.5737</v>
+        <v>126.5389</v>
       </c>
       <c r="H97" t="n">
-        <v>240.6538</v>
+        <v>232.9441</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9842</v>
+        <v>0.9806</v>
       </c>
       <c r="F98" t="n">
-        <v>1.3358</v>
+        <v>0.6357</v>
       </c>
       <c r="G98" t="n">
-        <v>76.3492</v>
+        <v>78.7782</v>
       </c>
       <c r="H98" t="n">
-        <v>208.9743</v>
+        <v>212.0041</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9823</v>
+        <v>0.9694</v>
       </c>
       <c r="F99" t="n">
-        <v>1.3478</v>
+        <v>0.6354</v>
       </c>
       <c r="G99" t="n">
-        <v>79.6142</v>
+        <v>95.7148</v>
       </c>
       <c r="H99" t="n">
-        <v>212.6565</v>
+        <v>212.0833</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9826</v>
+        <v>0.9788</v>
       </c>
       <c r="F100" t="n">
-        <v>1.3381</v>
+        <v>0.6473</v>
       </c>
       <c r="G100" t="n">
-        <v>79.2786</v>
+        <v>79.1268</v>
       </c>
       <c r="H100" t="n">
-        <v>209.6822</v>
+        <v>208.6075</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9837</v>
+        <v>0.9774</v>
       </c>
       <c r="F101" t="n">
-        <v>1.3535</v>
+        <v>0.6428</v>
       </c>
       <c r="G101" t="n">
-        <v>75.9593</v>
+        <v>81.0463</v>
       </c>
       <c r="H101" t="n">
-        <v>214.3939</v>
+        <v>209.9226</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9836</v>
+        <v>0.9785</v>
       </c>
       <c r="F102" t="n">
-        <v>1.3576</v>
+        <v>0.6421</v>
       </c>
       <c r="G102" t="n">
-        <v>77.1332</v>
+        <v>79.0577</v>
       </c>
       <c r="H102" t="n">
-        <v>215.6439</v>
+        <v>210.1124</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9749</v>
+        <v>0.9825</v>
       </c>
       <c r="F103" t="n">
-        <v>1.3618</v>
+        <v>0.653</v>
       </c>
       <c r="G103" t="n">
-        <v>92.40689999999999</v>
+        <v>78.967</v>
       </c>
       <c r="H103" t="n">
-        <v>216.9149</v>
+        <v>206.9145</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.982</v>
+        <v>0.9809</v>
       </c>
       <c r="F104" t="n">
-        <v>1.3348</v>
+        <v>0.633</v>
       </c>
       <c r="G104" t="n">
-        <v>79.4657</v>
+        <v>79.79600000000001</v>
       </c>
       <c r="H104" t="n">
-        <v>208.6535</v>
+        <v>212.7862</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9832</v>
+        <v>0.9692</v>
       </c>
       <c r="F105" t="n">
-        <v>1.3434</v>
+        <v>0.6409</v>
       </c>
       <c r="G105" t="n">
-        <v>78.9911</v>
+        <v>94.88509999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>211.321</v>
+        <v>210.479</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9827</v>
+        <v>0.9699</v>
       </c>
       <c r="F106" t="n">
-        <v>1.3506</v>
+        <v>0.6501</v>
       </c>
       <c r="G106" t="n">
-        <v>78.9289</v>
+        <v>94.4666</v>
       </c>
       <c r="H106" t="n">
-        <v>213.511</v>
+        <v>207.7625</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9819</v>
+        <v>0.9669</v>
       </c>
       <c r="F107" t="n">
-        <v>1.3484</v>
+        <v>0.65</v>
       </c>
       <c r="G107" t="n">
-        <v>79.1541</v>
+        <v>97.7657</v>
       </c>
       <c r="H107" t="n">
-        <v>212.8529</v>
+        <v>207.8048</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9837</v>
+        <v>0.9588</v>
       </c>
       <c r="F108" t="n">
-        <v>1.3653</v>
+        <v>0.6075</v>
       </c>
       <c r="G108" t="n">
-        <v>80.017</v>
+        <v>115.0461</v>
       </c>
       <c r="H108" t="n">
-        <v>217.9581</v>
+        <v>220.0589</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9852</v>
+        <v>0.9749</v>
       </c>
       <c r="F109" t="n">
-        <v>1.3392</v>
+        <v>0.6353</v>
       </c>
       <c r="G109" t="n">
-        <v>76.0629</v>
+        <v>89.26300000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>210.014</v>
+        <v>212.1231</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9817</v>
+        <v>0.9761</v>
       </c>
       <c r="F110" t="n">
-        <v>1.3088</v>
+        <v>0.6508</v>
       </c>
       <c r="G110" t="n">
-        <v>79.08280000000001</v>
+        <v>84.9306</v>
       </c>
       <c r="H110" t="n">
-        <v>200.3983</v>
+        <v>207.5545</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9832</v>
+        <v>0.9725</v>
       </c>
       <c r="F111" t="n">
-        <v>1.3213</v>
+        <v>0.6288</v>
       </c>
       <c r="G111" t="n">
-        <v>75.1728</v>
+        <v>91.10339999999999</v>
       </c>
       <c r="H111" t="n">
-        <v>204.4003</v>
+        <v>213.9998</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9843</v>
+        <v>0.9748</v>
       </c>
       <c r="F112" t="n">
-        <v>1.3604</v>
+        <v>0.6142</v>
       </c>
       <c r="G112" t="n">
-        <v>79.026</v>
+        <v>90.9855</v>
       </c>
       <c r="H112" t="n">
-        <v>216.4683</v>
+        <v>218.1773</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9858</v>
+        <v>0.9751</v>
       </c>
       <c r="F113" t="n">
-        <v>1.334</v>
+        <v>0.6357</v>
       </c>
       <c r="G113" t="n">
-        <v>75.16840000000001</v>
+        <v>88.97750000000001</v>
       </c>
       <c r="H113" t="n">
-        <v>208.4015</v>
+        <v>211.9874</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9817</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F114" t="n">
-        <v>1.3093</v>
+        <v>0.6511</v>
       </c>
       <c r="G114" t="n">
-        <v>79.31789999999999</v>
+        <v>84.92100000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>200.5555</v>
+        <v>207.4533</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9823</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="F115" t="n">
-        <v>1.3292</v>
+        <v>0.6242</v>
       </c>
       <c r="G115" t="n">
-        <v>76.8205</v>
+        <v>108.3976</v>
       </c>
       <c r="H115" t="n">
-        <v>206.9118</v>
+        <v>215.3141</v>
       </c>
     </row>
     <row r="116">
@@ -4126,16 +4126,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8433</v>
+        <v>0.8202</v>
       </c>
       <c r="F116" t="n">
-        <v>1.8349</v>
+        <v>0.1102</v>
       </c>
       <c r="G116" t="n">
-        <v>215.4715</v>
+        <v>223.0477</v>
       </c>
       <c r="H116" t="n">
-        <v>329.4887</v>
+        <v>331.3202</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8839</v>
+        <v>0.8239</v>
       </c>
       <c r="F117" t="n">
-        <v>1.8447</v>
+        <v>0.1008</v>
       </c>
       <c r="G117" t="n">
-        <v>192.3805</v>
+        <v>221.5415</v>
       </c>
       <c r="H117" t="n">
-        <v>331.4326</v>
+        <v>333.0682</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9832</v>
+        <v>0.9692</v>
       </c>
       <c r="F118" t="n">
-        <v>1.3434</v>
+        <v>0.6409</v>
       </c>
       <c r="G118" t="n">
-        <v>78.9911</v>
+        <v>94.88509999999999</v>
       </c>
       <c r="H118" t="n">
-        <v>211.321</v>
+        <v>210.479</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9858</v>
+        <v>0.9751</v>
       </c>
       <c r="F119" t="n">
-        <v>1.334</v>
+        <v>0.6357</v>
       </c>
       <c r="G119" t="n">
-        <v>75.16840000000001</v>
+        <v>88.97750000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>208.4015</v>
+        <v>211.9874</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F120" t="n">
-        <v>1.3383</v>
+        <v>0.6592</v>
       </c>
       <c r="G120" t="n">
-        <v>116.943</v>
+        <v>122.4071</v>
       </c>
       <c r="H120" t="n">
-        <v>209.7527</v>
+        <v>205.0544</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F121" t="n">
-        <v>1.3383</v>
+        <v>0.6592</v>
       </c>
       <c r="G121" t="n">
-        <v>116.943</v>
+        <v>122.4071</v>
       </c>
       <c r="H121" t="n">
-        <v>209.7527</v>
+        <v>205.0544</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9853</v>
+        <v>0.9552</v>
       </c>
       <c r="F122" t="n">
-        <v>1.26</v>
+        <v>0.6869</v>
       </c>
       <c r="G122" t="n">
-        <v>67.282</v>
+        <v>107.9957</v>
       </c>
       <c r="H122" t="n">
-        <v>183.8576</v>
+        <v>196.5225</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9858</v>
+        <v>0.9751</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3356</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>75.6384</v>
+        <v>88.992</v>
       </c>
       <c r="H123" t="n">
-        <v>208.9034</v>
+        <v>212.0242</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9865</v>
+        <v>0.9767</v>
       </c>
       <c r="F124" t="n">
-        <v>1.3367</v>
+        <v>0.6574</v>
       </c>
       <c r="G124" t="n">
-        <v>74.0454</v>
+        <v>85.7608</v>
       </c>
       <c r="H124" t="n">
-        <v>209.2376</v>
+        <v>205.5795</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9656</v>
       </c>
       <c r="F125" t="n">
-        <v>1.4459</v>
+        <v>0.5589</v>
       </c>
       <c r="G125" t="n">
-        <v>100.2053</v>
+        <v>101.078</v>
       </c>
       <c r="H125" t="n">
-        <v>240.7978</v>
+        <v>233.2667</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9786</v>
+        <v>0.9756</v>
       </c>
       <c r="F126" t="n">
-        <v>1.3049</v>
+        <v>0.6767</v>
       </c>
       <c r="G126" t="n">
-        <v>81.2277</v>
+        <v>84.8841</v>
       </c>
       <c r="H126" t="n">
-        <v>199.1046</v>
+        <v>199.7005</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.7876</v>
+        <v>0.8653</v>
       </c>
       <c r="F127" t="n">
-        <v>1.9611</v>
+        <v>0.0319</v>
       </c>
       <c r="G127" t="n">
-        <v>238.9323</v>
+        <v>203.0635</v>
       </c>
       <c r="H127" t="n">
-        <v>353.5263</v>
+        <v>345.597</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9774</v>
+        <v>0.9697</v>
       </c>
       <c r="F128" t="n">
-        <v>1.3082</v>
+        <v>0.6786</v>
       </c>
       <c r="G128" t="n">
-        <v>82.5391</v>
+        <v>90.65300000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>200.1882</v>
+        <v>199.1362</v>
       </c>
     </row>
     <row r="129">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9807</v>
       </c>
       <c r="F129" t="n">
-        <v>1.308</v>
+        <v>0.6781</v>
       </c>
       <c r="G129" t="n">
-        <v>82.48269999999999</v>
+        <v>75.1066</v>
       </c>
       <c r="H129" t="n">
-        <v>200.1315</v>
+        <v>199.2814</v>
       </c>
     </row>
     <row r="130">
@@ -4574,16 +4574,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9771</v>
+        <v>0.9742</v>
       </c>
       <c r="F130" t="n">
-        <v>1.3122</v>
+        <v>0.6681</v>
       </c>
       <c r="G130" t="n">
-        <v>83.0489</v>
+        <v>86.08150000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>201.4761</v>
+        <v>202.3489</v>
       </c>
     </row>
     <row r="131">
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9772</v>
+        <v>0.9741</v>
       </c>
       <c r="F131" t="n">
-        <v>1.3096</v>
+        <v>0.6661</v>
       </c>
       <c r="G131" t="n">
-        <v>82.77419999999999</v>
+        <v>86.3021</v>
       </c>
       <c r="H131" t="n">
-        <v>200.6486</v>
+        <v>202.945</v>
       </c>
     </row>
     <row r="132">
@@ -4638,16 +4638,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9848</v>
+        <v>0.9816</v>
       </c>
       <c r="F132" t="n">
-        <v>1.3007</v>
+        <v>0.6861</v>
       </c>
       <c r="G132" t="n">
-        <v>70.19029999999999</v>
+        <v>74.3925</v>
       </c>
       <c r="H132" t="n">
-        <v>197.731</v>
+        <v>196.79</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9835</v>
+        <v>0.9755</v>
       </c>
       <c r="F133" t="n">
-        <v>1.3057</v>
+        <v>0.6823</v>
       </c>
       <c r="G133" t="n">
-        <v>71.7961</v>
+        <v>83.8061</v>
       </c>
       <c r="H133" t="n">
-        <v>199.3757</v>
+        <v>197.9607</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9779</v>
+        <v>0.9696</v>
       </c>
       <c r="F134" t="n">
-        <v>1.3066</v>
+        <v>0.6797</v>
       </c>
       <c r="G134" t="n">
-        <v>81.6867</v>
+        <v>90.295</v>
       </c>
       <c r="H134" t="n">
-        <v>199.6845</v>
+        <v>198.7839</v>
       </c>
     </row>
     <row r="135">
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9776</v>
+        <v>0.9746</v>
       </c>
       <c r="F135" t="n">
-        <v>1.308</v>
+        <v>0.6804</v>
       </c>
       <c r="G135" t="n">
-        <v>82.2086</v>
+        <v>85.2976</v>
       </c>
       <c r="H135" t="n">
-        <v>200.1325</v>
+        <v>198.5703</v>
       </c>
     </row>
     <row r="136">
@@ -4766,16 +4766,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9774</v>
+        <v>0.9737</v>
       </c>
       <c r="F136" t="n">
-        <v>1.3086</v>
+        <v>0.6673</v>
       </c>
       <c r="G136" t="n">
-        <v>82.4747</v>
+        <v>86.6994</v>
       </c>
       <c r="H136" t="n">
-        <v>200.3094</v>
+        <v>202.5865</v>
       </c>
     </row>
     <row r="137">
@@ -4794,20 +4794,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9791</v>
+        <v>0.9737</v>
       </c>
       <c r="F137" t="n">
-        <v>1.3036</v>
+        <v>0.6893</v>
       </c>
       <c r="G137" t="n">
-        <v>80.8704</v>
+        <v>85.96850000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>198.7059</v>
+        <v>195.7744</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9861</v>
+        <v>0.9787</v>
       </c>
       <c r="F138" t="n">
-        <v>1.3068</v>
+        <v>0.6926</v>
       </c>
       <c r="G138" t="n">
-        <v>68.3527</v>
+        <v>79.0575</v>
       </c>
       <c r="H138" t="n">
-        <v>199.7458</v>
+        <v>194.7526</v>
       </c>
     </row>
     <row r="139">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9862</v>
+        <v>0.9828</v>
       </c>
       <c r="F139" t="n">
-        <v>1.3082</v>
+        <v>0.6803</v>
       </c>
       <c r="G139" t="n">
-        <v>68.35290000000001</v>
+        <v>71.7239</v>
       </c>
       <c r="H139" t="n">
-        <v>200.1827</v>
+        <v>198.5833</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9804</v>
+        <v>0.9863</v>
       </c>
       <c r="F140" t="n">
-        <v>1.2963</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G140" t="n">
-        <v>81.4551</v>
+        <v>68.0343</v>
       </c>
       <c r="H140" t="n">
-        <v>196.2966</v>
+        <v>196.8194</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9801</v>
+        <v>0.9838</v>
       </c>
       <c r="F141" t="n">
-        <v>1.2908</v>
+        <v>0.6983</v>
       </c>
       <c r="G141" t="n">
-        <v>81.9294</v>
+        <v>70.9529</v>
       </c>
       <c r="H141" t="n">
-        <v>194.4432</v>
+        <v>192.9337</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9861</v>
+        <v>0.9787</v>
       </c>
       <c r="F142" t="n">
-        <v>1.3068</v>
+        <v>0.6926</v>
       </c>
       <c r="G142" t="n">
-        <v>68.3527</v>
+        <v>79.0575</v>
       </c>
       <c r="H142" t="n">
-        <v>199.7458</v>
+        <v>194.7526</v>
       </c>
     </row>
     <row r="143">
@@ -4986,20 +4986,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9863</v>
+        <v>0.9762</v>
       </c>
       <c r="F143" t="n">
-        <v>1.3039</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G143" t="n">
-        <v>67.7602</v>
+        <v>83.2923</v>
       </c>
       <c r="H143" t="n">
-        <v>198.7855</v>
+        <v>197.4575</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9849</v>
+        <v>0.9728</v>
       </c>
       <c r="F144" t="n">
-        <v>1.2986</v>
+        <v>0.6871</v>
       </c>
       <c r="G144" t="n">
-        <v>70.9256</v>
+        <v>86.4127</v>
       </c>
       <c r="H144" t="n">
-        <v>197.0597</v>
+        <v>196.4862</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9801</v>
+        <v>0.9838</v>
       </c>
       <c r="F145" t="n">
-        <v>1.2908</v>
+        <v>0.6983</v>
       </c>
       <c r="G145" t="n">
-        <v>81.9294</v>
+        <v>70.9529</v>
       </c>
       <c r="H145" t="n">
-        <v>194.4432</v>
+        <v>192.9337</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.7882</v>
+        <v>0.8675</v>
       </c>
       <c r="F146" t="n">
-        <v>1.9624</v>
+        <v>0.0236</v>
       </c>
       <c r="G146" t="n">
-        <v>238.3036</v>
+        <v>202.1734</v>
       </c>
       <c r="H146" t="n">
-        <v>353.7653</v>
+        <v>347.073</v>
       </c>
     </row>
     <row r="147">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.79</v>
+        <v>0.8689</v>
       </c>
       <c r="F147" t="n">
-        <v>1.9612</v>
+        <v>0.0311</v>
       </c>
       <c r="G147" t="n">
-        <v>237.7503</v>
+        <v>201.5097</v>
       </c>
       <c r="H147" t="n">
-        <v>353.5388</v>
+        <v>345.7291</v>
       </c>
     </row>
     <row r="148">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.7895</v>
+        <v>0.8704</v>
       </c>
       <c r="F148" t="n">
-        <v>1.9593</v>
+        <v>0.0371</v>
       </c>
       <c r="G148" t="n">
-        <v>238.2072</v>
+        <v>200.8463</v>
       </c>
       <c r="H148" t="n">
-        <v>353.1922</v>
+        <v>344.6576</v>
       </c>
     </row>
     <row r="149">
@@ -5178,20 +5178,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.7907</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="F149" t="n">
-        <v>1.9592</v>
+        <v>0.0276</v>
       </c>
       <c r="G149" t="n">
-        <v>237.7169</v>
+        <v>202.144</v>
       </c>
       <c r="H149" t="n">
-        <v>353.1731</v>
+        <v>346.3588</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.8655</v>
       </c>
       <c r="F150" t="n">
-        <v>1.9624</v>
+        <v>0.0324</v>
       </c>
       <c r="G150" t="n">
-        <v>238.3628</v>
+        <v>202.7452</v>
       </c>
       <c r="H150" t="n">
-        <v>353.7547</v>
+        <v>345.5</v>
       </c>
     </row>
     <row r="151">
@@ -5242,20 +5242,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.8656</v>
       </c>
       <c r="F151" t="n">
-        <v>1.963</v>
+        <v>0.0309</v>
       </c>
       <c r="G151" t="n">
-        <v>238.3192</v>
+        <v>202.5888</v>
       </c>
       <c r="H151" t="n">
-        <v>353.8684</v>
+        <v>345.7662</v>
       </c>
     </row>
     <row r="152">
@@ -5274,20 +5274,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.7896</v>
+        <v>0.8656</v>
       </c>
       <c r="F152" t="n">
-        <v>1.963</v>
+        <v>0.0291</v>
       </c>
       <c r="G152" t="n">
-        <v>237.8898</v>
+        <v>202.7963</v>
       </c>
       <c r="H152" t="n">
-        <v>353.8741</v>
+        <v>346.0824</v>
       </c>
     </row>
     <row r="153">
@@ -5306,20 +5306,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.7903</v>
+        <v>0.8679</v>
       </c>
       <c r="F153" t="n">
-        <v>1.9621</v>
+        <v>0.0286</v>
       </c>
       <c r="G153" t="n">
-        <v>237.6603</v>
+        <v>201.6272</v>
       </c>
       <c r="H153" t="n">
-        <v>353.7078</v>
+        <v>346.1761</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.7891</v>
+        <v>0.8668</v>
       </c>
       <c r="F154" t="n">
-        <v>1.9547</v>
+        <v>0.0319</v>
       </c>
       <c r="G154" t="n">
-        <v>238.2105</v>
+        <v>202.4595</v>
       </c>
       <c r="H154" t="n">
-        <v>352.337</v>
+        <v>345.587</v>
       </c>
     </row>
     <row r="155">
@@ -5370,20 +5370,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.9042</v>
+        <v>0.8691</v>
       </c>
       <c r="F155" t="n">
-        <v>1.7918</v>
+        <v>0.096</v>
       </c>
       <c r="G155" t="n">
-        <v>179.1117</v>
+        <v>200.8074</v>
       </c>
       <c r="H155" t="n">
-        <v>320.8706</v>
+        <v>333.9557</v>
       </c>
     </row>
     <row r="156">
@@ -5402,20 +5402,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9102</v>
+        <v>0.9436</v>
       </c>
       <c r="F156" t="n">
-        <v>1.8025</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>172.9713</v>
+        <v>148.139</v>
       </c>
       <c r="H156" t="n">
-        <v>323.0295</v>
+        <v>335.0043</v>
       </c>
     </row>
     <row r="157">
@@ -5434,20 +5434,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9063</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="F157" t="n">
-        <v>1.812</v>
+        <v>0.0907</v>
       </c>
       <c r="G157" t="n">
-        <v>175.1256</v>
+        <v>189.4885</v>
       </c>
       <c r="H157" t="n">
-        <v>324.9524</v>
+        <v>334.9356</v>
       </c>
     </row>
     <row r="158">
@@ -5466,20 +5466,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.878</v>
+        <v>0.9512</v>
       </c>
       <c r="F158" t="n">
-        <v>1.8083</v>
+        <v>0.1332</v>
       </c>
       <c r="G158" t="n">
-        <v>200.4145</v>
+        <v>144.4205</v>
       </c>
       <c r="H158" t="n">
-        <v>324.2083</v>
+        <v>327.0064</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.986</v>
+        <v>0.9769</v>
       </c>
       <c r="F159" t="n">
-        <v>1.2784</v>
+        <v>0.6888</v>
       </c>
       <c r="G159" t="n">
-        <v>67.0766</v>
+        <v>81.45229999999999</v>
       </c>
       <c r="H159" t="n">
-        <v>190.2741</v>
+        <v>195.9258</v>
       </c>
     </row>
     <row r="160">
@@ -5530,20 +5530,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.7933</v>
       </c>
       <c r="F160" t="n">
-        <v>1.8847</v>
+        <v>0.0403</v>
       </c>
       <c r="G160" t="n">
-        <v>197.9142</v>
+        <v>233.9483</v>
       </c>
       <c r="H160" t="n">
-        <v>339.1699</v>
+        <v>344.0947</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8729</v>
+        <v>0.8642</v>
       </c>
       <c r="F161" t="n">
-        <v>1.8953</v>
+        <v>0.0399</v>
       </c>
       <c r="G161" t="n">
-        <v>198.1167</v>
+        <v>200.9215</v>
       </c>
       <c r="H161" t="n">
-        <v>341.2114</v>
+        <v>344.1603</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9782</v>
+        <v>0.9764</v>
       </c>
       <c r="F162" t="n">
-        <v>1.2699</v>
+        <v>0.6911</v>
       </c>
       <c r="G162" t="n">
-        <v>81.43689999999999</v>
+        <v>82.315</v>
       </c>
       <c r="H162" t="n">
-        <v>187.3425</v>
+        <v>195.2147</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9808</v>
+        <v>0.9856</v>
       </c>
       <c r="F163" t="n">
-        <v>1.2896</v>
+        <v>0.6828</v>
       </c>
       <c r="G163" t="n">
-        <v>78.1712</v>
+        <v>69.1001</v>
       </c>
       <c r="H163" t="n">
-        <v>194.0708</v>
+        <v>197.8141</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9804</v>
+        <v>0.9863</v>
       </c>
       <c r="F164" t="n">
-        <v>1.2964</v>
+        <v>0.6851</v>
       </c>
       <c r="G164" t="n">
-        <v>81.45780000000001</v>
+        <v>67.98569999999999</v>
       </c>
       <c r="H164" t="n">
-        <v>196.3186</v>
+        <v>197.0983</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9656</v>
       </c>
       <c r="F165" t="n">
-        <v>1.4459</v>
+        <v>0.5589</v>
       </c>
       <c r="G165" t="n">
-        <v>100.2053</v>
+        <v>101.078</v>
       </c>
       <c r="H165" t="n">
-        <v>240.7978</v>
+        <v>233.2667</v>
       </c>
     </row>
     <row r="166">
@@ -5726,16 +5726,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7937</v>
+        <v>0.758</v>
       </c>
       <c r="F166" t="n">
-        <v>2.1058</v>
+        <v>-0.0891</v>
       </c>
       <c r="G166" t="n">
-        <v>256.5079</v>
+        <v>257.5956</v>
       </c>
       <c r="H166" t="n">
-        <v>379.2027</v>
+        <v>366.5515</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9771</v>
+        <v>0.9726</v>
       </c>
       <c r="F167" t="n">
-        <v>1.3092</v>
+        <v>0.697</v>
       </c>
       <c r="G167" t="n">
-        <v>83.23520000000001</v>
+        <v>85.5354</v>
       </c>
       <c r="H167" t="n">
-        <v>200.5324</v>
+        <v>193.331</v>
       </c>
     </row>
     <row r="168">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9869</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F168" t="n">
-        <v>1.2875</v>
+        <v>0.7024</v>
       </c>
       <c r="G168" t="n">
-        <v>67.7345</v>
+        <v>83.35760000000001</v>
       </c>
       <c r="H168" t="n">
-        <v>193.3371</v>
+        <v>191.6176</v>
       </c>
     </row>
     <row r="169">
@@ -5822,16 +5822,16 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9856</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F169" t="n">
-        <v>1.3238</v>
+        <v>0.6804</v>
       </c>
       <c r="G169" t="n">
-        <v>70.9252</v>
+        <v>75.8706</v>
       </c>
       <c r="H169" t="n">
-        <v>205.1854</v>
+        <v>198.5649</v>
       </c>
     </row>
     <row r="170">
@@ -5854,16 +5854,16 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9791</v>
+        <v>0.9717</v>
       </c>
       <c r="F170" t="n">
-        <v>1.3555</v>
+        <v>0.6677</v>
       </c>
       <c r="G170" t="n">
-        <v>86.00060000000001</v>
+        <v>91.5117</v>
       </c>
       <c r="H170" t="n">
-        <v>215.0183</v>
+        <v>202.4822</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9836</v>
+        <v>0.9755</v>
       </c>
       <c r="F171" t="n">
-        <v>1.3424</v>
+        <v>0.6937</v>
       </c>
       <c r="G171" t="n">
-        <v>74.48860000000001</v>
+        <v>83.1533</v>
       </c>
       <c r="H171" t="n">
-        <v>211.0028</v>
+        <v>194.4011</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9851</v>
+        <v>0.9799</v>
       </c>
       <c r="F172" t="n">
-        <v>1.296</v>
+        <v>0.6979</v>
       </c>
       <c r="G172" t="n">
-        <v>69.51220000000001</v>
+        <v>79.6707</v>
       </c>
       <c r="H172" t="n">
-        <v>196.1808</v>
+        <v>193.0505</v>
       </c>
     </row>
   </sheetData>
